--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>9597</v>
+        <v>9604</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>10.89</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>881.2672176308539</v>
+        <v>881.1009174311927</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.07295218549430937</v>
+        <v>0.07304903595525114</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.09182736455463728</v>
+        <v>0.09174311926605504</v>
       </c>
     </row>
     <row r="8">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>49.18087419772375</v>
+        <v>49.21961438210045</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>41.79971680477166</v>
+        <v>41.81133886008467</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>7.157042502201678</v>
+        <v>7.158229612137221</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6307.266932381038</v>
+        <v>6307.122678437237</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>-0.3427876490172931</v>
+        <v>-0.3432816869598879</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>11.06575292407945</v>
+        <v>11.06683211492994</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9751.885290393981</v>
+        <v>9750.995929521758</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.01613892783098692</v>
+        <v>0.01530569861742581</v>
       </c>
     </row>
     <row r="15"/>
@@ -4205,7 +4205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4296,6 +4296,39 @@
       </c>
       <c r="I2">
         <f>IF(H2="","",IF(H2&gt;=70,"BUY",IF(H2&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>9604</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>0.613636363636</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0.0730490359553</v>
+      </c>
+      <c r="F3" s="22">
+        <f>IF(D3="","",100*(1-D3))</f>
+        <v/>
+      </c>
+      <c r="G3" s="22">
+        <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H3" s="22">
+        <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>9604</v>
+        <v>9616.700000000001</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>10.9</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>881.1009174311927</v>
+        <v>881.4573785517874</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.07304903595525114</v>
+        <v>0.07300377944707193</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.09174311926605504</v>
+        <v>0.09165902841429881</v>
       </c>
     </row>
     <row r="8">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>49.21961438210045</v>
+        <v>49.20151177882877</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>41.81133886008467</v>
+        <v>41.80590807910318</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>7.158229612137221</v>
+        <v>7.157674896651253</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6307.122678437237</v>
+        <v>6309.185350928149</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>-0.3432816869598879</v>
+        <v>-0.3439344732675296</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>11.06683211492994</v>
+        <v>11.06632782812451</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9750.995929521758</v>
+        <v>9754.49631757333</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.01530569861742581</v>
+        <v>0.01432885684001062</v>
       </c>
     </row>
     <row r="15"/>
@@ -4205,7 +4205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4329,6 +4329,39 @@
       </c>
       <c r="I3">
         <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>9616.700000000001</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>0.613636363636</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0.0730037794471</v>
+      </c>
+      <c r="F4" s="22">
+        <f>IF(D4="","",100*(1-D4))</f>
+        <v/>
+      </c>
+      <c r="G4" s="22">
+        <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,17 +21,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;[Red](#,##0.00);-"/>
-    <numFmt numFmtId="167" formatCode="0.00x;[Red](0.00x);-"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0;[Red](#,##0.0);-"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="0.00x"/>
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;[Red](#,##0.00);-"/>
+    <numFmt numFmtId="166" formatCode="0.00x;[Red](0.00x);-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;[Red](#,##0.0);-"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +67,11 @@
       <color theme="10"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
     </font>
   </fonts>
   <fills count="5">
@@ -105,36 +110,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -566,7 +584,7 @@
           <t>As of</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="23" t="n">
         <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -580,7 +598,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -594,7 +611,7 @@
           <t>Index level</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>9616.700000000001</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -602,7 +619,7 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="25" t="n">
         <v>10.91</v>
       </c>
     </row>
@@ -612,7 +629,7 @@
           <t>P/E percentile</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="26" t="n">
         <v>0.6136363636363636</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -620,7 +637,7 @@
           <t>Implied EPS</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="27" t="n">
         <v>881.4573785517874</v>
       </c>
     </row>
@@ -630,7 +647,7 @@
           <t>YoY implied EPS growth</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="26" t="n">
         <v>0.07300377944707193</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -648,7 +665,7 @@
           <t>Valuation score</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="28" t="n">
         <v>38.63636363636363</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -656,7 +673,7 @@
           <t>Growth score</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="28" t="n">
         <v>49.20151177882877</v>
       </c>
     </row>
@@ -666,7 +683,7 @@
           <t>Composite score</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="28" t="n">
         <v>41.80590807910318</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -680,7 +697,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -716,13 +732,13 @@
           <t>BUY → HOLD</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="29" t="n">
         <v>7.157674896651253</v>
       </c>
       <c r="C13" s="15" t="n">
         <v>6309.185350928149</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="30" t="n">
         <v>-0.3439344732675296</v>
       </c>
     </row>
@@ -732,17 +748,16 @@
           <t>HOLD → SELL</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="29" t="n">
         <v>11.06632782812451</v>
       </c>
       <c r="C14" s="15" t="n">
         <v>9754.49631757333</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="30" t="n">
         <v>0.01432885684001062</v>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -796,17 +811,17 @@
       <c r="B18" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="30" t="n">
         <v>0.365306703084248</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="30" t="n">
         <v>0.3332954276386275</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="30" t="n">
         <v>0.328147655909417</v>
       </c>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="16" t="n">
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -819,19 +834,19 @@
       <c r="B19" t="n">
         <v>8</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="30" t="n">
         <v>0.214735699669954</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="30" t="n">
         <v>0.299789514883279</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="30" t="n">
         <v>0.2255865728794684</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="30" t="n">
         <v>0.1287781696551022</v>
       </c>
-      <c r="G19" s="16" t="n">
+      <c r="G19" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -844,17 +859,17 @@
       <c r="B20" t="n">
         <v>9</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="30" t="n">
         <v>0.1251624476057706</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="30" t="n">
         <v>0.0462515327216334</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="30" t="n">
         <v>0.205400318169531</v>
       </c>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="16" t="n">
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -867,19 +882,19 @@
       <c r="B21" t="n">
         <v>8</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="30" t="n">
         <v>-0.01560536424732312</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="30" t="n">
         <v>-0.02126125583912941</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="30" t="n">
         <v>0.01435009279235056</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="30" t="n">
         <v>0.1215161733022436</v>
       </c>
-      <c r="G21" s="16" t="n">
+      <c r="G21" s="30" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -892,21 +907,20 @@
       <c r="B22" t="n">
         <v>10</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="30" t="n">
         <v>-0.01119020374195645</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="30" t="n">
         <v>-0.1337621850380084</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="30" t="n">
         <v>0.003776895891633769</v>
       </c>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="16" t="n">
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
@@ -1042,16 +1056,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>44316</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>3175.85</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>9.81</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="32">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
@@ -1061,16 +1075,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>44347</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>3516.75</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>8.5</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="32">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
@@ -1080,16 +1094,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>3609.45</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>7.35</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="32">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
@@ -1099,16 +1113,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>44408</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>3584.95</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>7.29</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="32">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
@@ -1118,16 +1132,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>44439</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>3646.4</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>6.36</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="32">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
@@ -1137,16 +1151,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>4096.7</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>7.06</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="32">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
@@ -1156,16 +1170,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>44500</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>4005.65</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>6.9</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="32">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
@@ -1175,16 +1189,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>44530</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>3820.05</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>5.93</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="32">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
@@ -1194,16 +1208,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>3835.25</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>5.91</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="32">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
@@ -1213,16 +1227,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>44592</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>4156.35</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>6.4</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="32">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
@@ -1232,16 +1246,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>44620</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>3955.3</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>5.69</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="32">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
@@ -1251,16 +1265,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>4086.25</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>5.88</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="32">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
@@ -1270,16 +1284,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44681</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>4234.2</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>6.09</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="32">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
@@ -1289,16 +1303,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44712</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>4081.95</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>5.96</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="32">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
@@ -1308,16 +1322,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>3819.95</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>5.56</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="32">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
@@ -1327,16 +1341,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44773</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>4017.6</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>5.84</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="32">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
@@ -1346,16 +1360,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44804</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>4236.6</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>7.08</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="32">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
@@ -1365,16 +1379,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>3990.6</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>6.71</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="32">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
@@ -1384,16 +1398,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44865</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>4276.55</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>7.19</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="32">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
@@ -1403,16 +1417,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44895</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>4455.9</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>8.41</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="32">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
@@ -1422,16 +1436,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>4367</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>8.289999999999999</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="32">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
@@ -1441,16 +1455,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44957</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>4399.95</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>8.56</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="32">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
@@ -1460,16 +1474,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44985</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>4389.5</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>8.5</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="32">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
@@ -1479,16 +1493,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>4474</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>8.56</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="32">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
@@ -1498,16 +1512,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45046</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>4683.15</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>8.960000000000001</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="32">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
@@ -1517,16 +1531,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45077</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>4799.65</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>9.109999999999999</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="32">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
@@ -1536,16 +1550,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>5081.6</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>9.550000000000001</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="32">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
@@ -1555,16 +1569,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45138</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>5511.05</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>9.289999999999999</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="32">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
@@ -1574,16 +1588,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45169</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>5456.6</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>7.8</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="32">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
@@ -1593,16 +1607,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>5991.75</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>8.57</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="32">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
@@ -1612,16 +1626,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45230</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>5887.4</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>8.01</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="32">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
@@ -1631,16 +1645,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45260</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>6779.05</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>8.07</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="32">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
@@ -1650,16 +1664,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>7854.95</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>9.33</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="32">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
@@ -1669,16 +1683,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45322</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>8670.25</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="32">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
@@ -1688,16 +1702,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45351</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>9138.85</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>10.27</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="32">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
@@ -1707,16 +1721,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>9122.15</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>10.27</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="32">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
@@ -1726,16 +1740,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45412</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>9993.35</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>11.25</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="32">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
@@ -1745,16 +1759,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45443</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>10511.1</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>11.51</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="32">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
@@ -1764,16 +1778,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>10685.5</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>11.66</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="32">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
@@ -1783,16 +1797,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45504</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>11684.2</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>13.39</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="32">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
@@ -1802,16 +1816,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>45535</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>11493.6</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>13.43</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="32">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
@@ -1821,16 +1835,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>11286</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>13.31</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="32">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
@@ -1840,16 +1854,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>45596</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>10175.25</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>13.05</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="32">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
@@ -1859,16 +1873,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="n">
+      <c r="A45" s="31" t="n">
         <v>45626</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="24" t="n">
         <v>10121.45</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="25" t="n">
         <v>13.11</v>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="32">
         <f>IFERROR(B45/C45,"")</f>
         <v/>
       </c>
@@ -1878,16 +1892,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="n">
+      <c r="A46" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="24" t="n">
         <v>9532.200000000001</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="25" t="n">
         <v>12.35</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="32">
         <f>IFERROR(B46/C46,"")</f>
         <v/>
       </c>
@@ -1897,16 +1911,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="n">
+      <c r="A47" s="31" t="n">
         <v>45688</v>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="24" t="n">
         <v>9278.65</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="25" t="n">
         <v>12.13</v>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="32">
         <f>IFERROR(B47/C47,"")</f>
         <v/>
       </c>
@@ -1916,16 +1930,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="n">
+      <c r="A48" s="31" t="n">
         <v>45716</v>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" s="24" t="n">
         <v>8064.05</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="25" t="n">
         <v>10.43</v>
       </c>
-      <c r="D48" s="19">
+      <c r="D48" s="32">
         <f>IFERROR(B48/C48,"")</f>
         <v/>
       </c>
@@ -1935,16 +1949,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="n">
+      <c r="A49" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="24" t="n">
         <v>9342.700000000001</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="25" t="n">
         <v>12.17</v>
       </c>
-      <c r="D49" s="19">
+      <c r="D49" s="32">
         <f>IFERROR(B49/C49,"")</f>
         <v/>
       </c>
@@ -1954,16 +1968,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="n">
+      <c r="A50" s="31" t="n">
         <v>45777</v>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B50" s="24" t="n">
         <v>9559</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="25" t="n">
         <v>12.45</v>
       </c>
-      <c r="D50" s="19">
+      <c r="D50" s="32">
         <f>IFERROR(B50/C50,"")</f>
         <v/>
       </c>
@@ -1973,16 +1987,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="n">
+      <c r="A51" s="31" t="n">
         <v>45808</v>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="24" t="n">
         <v>9867.950000000001</v>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="25" t="n">
         <v>12.66</v>
       </c>
-      <c r="D51" s="19">
+      <c r="D51" s="32">
         <f>IFERROR(B51/C51,"")</f>
         <v/>
       </c>
@@ -1992,16 +2006,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="n">
+      <c r="A52" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B52" s="24" t="n">
         <v>10093.65</v>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C52" s="25" t="n">
         <v>12.94</v>
       </c>
-      <c r="D52" s="19">
+      <c r="D52" s="32">
         <f>IFERROR(B52/C52,"")</f>
         <v/>
       </c>
@@ -2011,16 +2025,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="n">
+      <c r="A53" s="31" t="n">
         <v>45869</v>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="24" t="n">
         <v>9682.700000000001</v>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="25" t="n">
         <v>12.35</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="32">
         <f>IFERROR(B53/C53,"")</f>
         <v/>
       </c>
@@ -2030,16 +2044,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="n">
+      <c r="A54" s="31" t="n">
         <v>45900</v>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="24" t="n">
         <v>9202.450000000001</v>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="25" t="n">
         <v>11.2</v>
       </c>
-      <c r="D54" s="19">
+      <c r="D54" s="32">
         <f>IFERROR(B54/C54,"")</f>
         <v/>
       </c>
@@ -2049,16 +2063,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="n">
+      <c r="A55" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="24" t="n">
         <v>9800.85</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="25" t="n">
         <v>11.93</v>
       </c>
-      <c r="D55" s="19">
+      <c r="D55" s="32">
         <f>IFERROR(B55/C55,"")</f>
         <v/>
       </c>
@@ -2068,16 +2082,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="n">
+      <c r="A56" s="31" t="n">
         <v>45961</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B56" s="24" t="n">
         <v>10062.95</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C56" s="25" t="n">
         <v>11.85</v>
       </c>
-      <c r="D56" s="19">
+      <c r="D56" s="32">
         <f>IFERROR(B56/C56,"")</f>
         <v/>
       </c>
@@ -2087,16 +2101,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="n">
+      <c r="A57" s="31" t="n">
         <v>45991</v>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B57" s="24" t="n">
         <v>9744.299999999999</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="25" t="n">
         <v>11.15</v>
       </c>
-      <c r="D57" s="19">
+      <c r="D57" s="32">
         <f>IFERROR(B57/C57,"")</f>
         <v/>
       </c>
@@ -2106,16 +2120,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="n">
+      <c r="A58" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B58" s="24" t="n">
         <v>9853.65</v>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="25" t="n">
         <v>11.23</v>
       </c>
-      <c r="D58" s="19">
+      <c r="D58" s="32">
         <f>IFERROR(B58/C58,"")</f>
         <v/>
       </c>
@@ -2125,16 +2139,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="n">
+      <c r="A59" s="31" t="n">
         <v>46053</v>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="24" t="n">
         <v>10171.25</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="25" t="n">
         <v>11.34</v>
       </c>
-      <c r="D59" s="19">
+      <c r="D59" s="32">
         <f>IFERROR(B59/C59,"")</f>
         <v/>
       </c>
@@ -2144,16 +2158,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="n">
+      <c r="A60" s="31" t="n">
         <v>46081</v>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B60" s="24" t="n">
         <v>10456.1</v>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C60" s="25" t="n">
         <v>11.34</v>
       </c>
-      <c r="D60" s="19">
+      <c r="D60" s="32">
         <f>IFERROR(B60/C60,"")</f>
         <v/>
       </c>
@@ -2163,16 +2177,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="n">
+      <c r="A61" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="24" t="n">
         <v>9559</v>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="25" t="n">
         <v>10.35</v>
       </c>
-      <c r="D61" s="19">
+      <c r="D61" s="32">
         <f>IFERROR(B61/C61,"")</f>
         <v/>
       </c>
@@ -2182,16 +2196,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="n">
+      <c r="A62" s="31" t="n">
         <v>46142</v>
       </c>
-      <c r="B62" s="6" t="n">
+      <c r="B62" s="24" t="n">
         <v>10629.05</v>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C62" s="25" t="n">
         <v>11.51</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="32">
         <f>IFERROR(B62/C62,"")</f>
         <v/>
       </c>
@@ -2201,16 +2215,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="n">
+      <c r="A63" s="31" t="n">
         <v>46173</v>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B63" s="24" t="n">
         <v>10227.35</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="25" t="n">
         <v>10.55</v>
       </c>
-      <c r="D63" s="19">
+      <c r="D63" s="32">
         <f>IFERROR(B63/C63,"")</f>
         <v/>
       </c>
@@ -2220,16 +2234,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="n">
+      <c r="A64" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B64" s="6" t="n">
+      <c r="B64" s="24" t="n">
         <v>9980.700000000001</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C64" s="25" t="n">
         <v>10.16</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="32">
         <f>IFERROR(B64/C64,"")</f>
         <v/>
       </c>
@@ -2239,16 +2253,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="n">
+      <c r="A65" s="31" t="n">
         <v>46234</v>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B65" s="24" t="n">
         <v>9941.9</v>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="25" t="n">
         <v>11.11</v>
       </c>
-      <c r="D65" s="19">
+      <c r="D65" s="32">
         <f>IFERROR(B65/C65,"")</f>
         <v/>
       </c>
@@ -2258,16 +2272,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="n">
+      <c r="A66" s="31" t="n">
         <v>46265</v>
       </c>
-      <c r="B66" s="6" t="n">
+      <c r="B66" s="24" t="n">
         <v>9704.4</v>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C66" s="25" t="n">
         <v>11.01</v>
       </c>
-      <c r="D66" s="19">
+      <c r="D66" s="32">
         <f>IFERROR(B66/C66,"")</f>
         <v/>
       </c>
@@ -2369,13 +2383,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>42369</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>3131.55</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>11.81</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2383,12 +2397,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="33">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16">
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30">
         <f>IF(C2="","",(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,C2)+1)/2)/COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2396,31 +2410,31 @@
         <f>IF(G2="","",IF(G2&lt;=20%,"Q1 Cheapest",IF(G2&lt;=40%,"Q2",IF(G2&lt;=60%,"Q3",IF(G2&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="30">
         <f>IFERROR(B6/B2-1,"")</f>
         <v/>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="30">
         <f>IFERROR((B14/B2)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="30">
         <f>IFERROR((B22/B2)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L2" s="16">
+      <c r="L2" s="30">
         <f>IFERROR((B42/B2)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>42460</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>2846.6</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>10.55</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2428,12 +2442,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="33">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="16">
+      <c r="F3" s="30" t="n"/>
+      <c r="G3" s="30">
         <f>IF(C3="","",(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,C3)+1)/2)/COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2441,31 +2455,31 @@
         <f>IF(G3="","",IF(G3&lt;=20%,"Q1 Cheapest",IF(G3&lt;=40%,"Q2",IF(G3&lt;=60%,"Q3",IF(G3&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="30">
         <f>IFERROR(B7/B3-1,"")</f>
         <v/>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="30">
         <f>IFERROR((B15/B3)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="30">
         <f>IFERROR((B23/B3)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="30">
         <f>IFERROR((B43/B3)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>42551</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>3168.75</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>12.15</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2473,12 +2487,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="33">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="16">
+      <c r="F4" s="30" t="n"/>
+      <c r="G4" s="30">
         <f>IF(C4="","",(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,C4)+1)/2)/COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2486,31 +2500,31 @@
         <f>IF(G4="","",IF(G4&lt;=20%,"Q1 Cheapest",IF(G4&lt;=40%,"Q2",IF(G4&lt;=60%,"Q3",IF(G4&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="30">
         <f>IFERROR(B8/B4-1,"")</f>
         <v/>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="30">
         <f>IFERROR((B16/B4)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="30">
         <f>IFERROR((B24/B4)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L4" s="16">
+      <c r="L4" s="30">
         <f>IFERROR((B44/B4)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>42643</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>3497.6</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>13.41</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2518,12 +2532,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="33">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="16">
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="30">
         <f>IF(C5="","",(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,C5)+1)/2)/COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2531,28 +2545,28 @@
         <f>IF(G5="","",IF(G5&lt;=20%,"Q1 Cheapest",IF(G5&lt;=40%,"Q2",IF(G5&lt;=60%,"Q3",IF(G5&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="30">
         <f>IFERROR(B9/B5-1,"")</f>
         <v/>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="30">
         <f>IFERROR((B17/B5)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="30">
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="16" t="n"/>
+      <c r="L5" s="30" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>42735</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>3692.7</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>12.95</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2560,15 +2574,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="33">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="30">
         <f>IF(AND(D6=D2,E2&lt;&gt;""),E6/E2-1,"")</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="30">
         <f>IF(C6="","",(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,C6)+1)/2)/COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2576,28 +2590,28 @@
         <f>IF(G6="","",IF(G6&lt;=20%,"Q1 Cheapest",IF(G6&lt;=40%,"Q2",IF(G6&lt;=60%,"Q3",IF(G6&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="30">
         <f>IFERROR(B10/B6-1,"")</f>
         <v/>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="30">
         <f>IFERROR((B18/B6)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="30">
         <f>IFERROR((B26/B6)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L6" s="16" t="n"/>
+      <c r="L6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>42825</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>4009.95</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>12.93</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2605,15 +2619,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="33">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="30">
         <f>IF(AND(D7=D3,E3&lt;&gt;""),E7/E3-1,"")</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="30">
         <f>IF(C7="","",(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,C7)+1)/2)/COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2621,28 +2635,28 @@
         <f>IF(G7="","",IF(G7&lt;=20%,"Q1 Cheapest",IF(G7&lt;=40%,"Q2",IF(G7&lt;=60%,"Q3",IF(G7&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="30">
         <f>IFERROR(B11/B7-1,"")</f>
         <v/>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="30">
         <f>IFERROR((B19/B7)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="30">
         <f>IFERROR((B27/B7)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L7" s="16" t="n"/>
+      <c r="L7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>42916</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>3776.05</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>12.37</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2650,15 +2664,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="33">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="30">
         <f>IF(AND(D8=D4,E4&lt;&gt;""),E8/E4-1,"")</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="30">
         <f>IF(C8="","",(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,C8)+1)/2)/COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2666,28 +2680,28 @@
         <f>IF(G8="","",IF(G8&lt;=20%,"Q1 Cheapest",IF(G8&lt;=40%,"Q2",IF(G8&lt;=60%,"Q3",IF(G8&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="30">
         <f>IFERROR(B12/B8-1,"")</f>
         <v/>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="30">
         <f>IFERROR((B20/B8)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="30">
         <f>IFERROR((B28/B8)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L8" s="16" t="n"/>
+      <c r="L8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>43008</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>4048.8</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>14.18</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2695,15 +2709,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="33">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="30">
         <f>IF(AND(D9=D5,E5&lt;&gt;""),E9/E5-1,"")</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="30">
         <f>IF(C9="","",(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,C9)+1)/2)/COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2711,28 +2725,28 @@
         <f>IF(G9="","",IF(G9&lt;=20%,"Q1 Cheapest",IF(G9&lt;=40%,"Q2",IF(G9&lt;=60%,"Q3",IF(G9&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="30">
         <f>IFERROR(B13/B9-1,"")</f>
         <v/>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="30">
         <f>IFERROR((B21/B9)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="30">
         <f>IFERROR((B29/B9)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L9" s="16" t="n"/>
+      <c r="L9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>43100</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>4303.25</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>14.64</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2740,15 +2754,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="33">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="30">
         <f>IF(AND(D10=D6,E6&lt;&gt;""),E10/E6-1,"")</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="30">
         <f>IF(C10="","",(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,C10)+1)/2)/COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2756,28 +2770,28 @@
         <f>IF(G10="","",IF(G10&lt;=20%,"Q1 Cheapest",IF(G10&lt;=40%,"Q2",IF(G10&lt;=60%,"Q3",IF(G10&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="30">
         <f>IFERROR(B14/B10-1,"")</f>
         <v/>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="30">
         <f>IFERROR((B22/B10)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="30">
         <f>IFERROR((B30/B10)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L10" s="16" t="n"/>
+      <c r="L10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>43190</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>3845.3</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>12.42</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2785,15 +2799,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="33">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="30">
         <f>IF(AND(D11=D7,E7&lt;&gt;""),E11/E7-1,"")</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="30">
         <f>IF(C11="","",(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,C11)+1)/2)/COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2801,28 +2815,28 @@
         <f>IF(G11="","",IF(G11&lt;=20%,"Q1 Cheapest",IF(G11&lt;=40%,"Q2",IF(G11&lt;=60%,"Q3",IF(G11&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="30">
         <f>IFERROR(B15/B11-1,"")</f>
         <v/>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="30">
         <f>IFERROR((B23/B11)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="30">
         <f>IFERROR((B31/B11)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L11" s="16" t="n"/>
+      <c r="L11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>43281</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>3527.45</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>10.94</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2830,15 +2844,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="33">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="30">
         <f>IF(AND(D12=D8,E8&lt;&gt;""),E12/E8-1,"")</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="30">
         <f>IF(C12="","",(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,C12)+1)/2)/COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2846,28 +2860,28 @@
         <f>IF(G12="","",IF(G12&lt;=20%,"Q1 Cheapest",IF(G12&lt;=40%,"Q2",IF(G12&lt;=60%,"Q3",IF(G12&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="30">
         <f>IFERROR(B16/B12-1,"")</f>
         <v/>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="30">
         <f>IFERROR((B24/B12)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="30">
         <f>IFERROR((B32/B12)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L12" s="16" t="n"/>
+      <c r="L12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>43373</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>3560.45</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>11</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2875,15 +2889,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="33">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="30">
         <f>IF(AND(D13=D9,E9&lt;&gt;""),E13/E9-1,"")</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="30">
         <f>IF(C13="","",(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,C13)+1)/2)/COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2891,28 +2905,28 @@
         <f>IF(G13="","",IF(G13&lt;=20%,"Q1 Cheapest",IF(G13&lt;=40%,"Q2",IF(G13&lt;=60%,"Q3",IF(G13&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="30">
         <f>IFERROR(B17/B13-1,"")</f>
         <v/>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="30">
         <f>IFERROR((B25/B13)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="30">
         <f>IFERROR((B33/B13)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L13" s="16" t="n"/>
+      <c r="L13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>43465</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>3389.35</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>10.62</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2920,15 +2934,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="33">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="30">
         <f>IF(AND(D14=D10,E10&lt;&gt;""),E14/E10-1,"")</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="30">
         <f>IF(C14="","",(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,C14)+1)/2)/COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2936,28 +2950,28 @@
         <f>IF(G14="","",IF(G14&lt;=20%,"Q1 Cheapest",IF(G14&lt;=40%,"Q2",IF(G14&lt;=60%,"Q3",IF(G14&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="30">
         <f>IFERROR(B18/B14-1,"")</f>
         <v/>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="30">
         <f>IFERROR((B26/B14)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="30">
         <f>IFERROR((B34/B14)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L14" s="16" t="n"/>
+      <c r="L14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>43555</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>3584.6</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>10.92</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2965,15 +2979,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="33">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="30">
         <f>IF(AND(D15=D11,E11&lt;&gt;""),E15/E11-1,"")</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="30">
         <f>IF(C15="","",(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,C15)+1)/2)/COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2981,28 +2995,28 @@
         <f>IF(G15="","",IF(G15&lt;=20%,"Q1 Cheapest",IF(G15&lt;=40%,"Q2",IF(G15&lt;=60%,"Q3",IF(G15&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="30">
         <f>IFERROR(B19/B15-1,"")</f>
         <v/>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="30">
         <f>IFERROR((B27/B15)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="30">
         <f>IFERROR((B35/B15)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L15" s="16" t="n"/>
+      <c r="L15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>43646</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>3657.25</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>10.72</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3010,15 +3024,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="33">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="30">
         <f>IF(AND(D16=D12,E12&lt;&gt;""),E16/E12-1,"")</f>
         <v/>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="30">
         <f>IF(C16="","",(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,C16)+1)/2)/COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3026,28 +3040,28 @@
         <f>IF(G16="","",IF(G16&lt;=20%,"Q1 Cheapest",IF(G16&lt;=40%,"Q2",IF(G16&lt;=60%,"Q3",IF(G16&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="30">
         <f>IFERROR(B20/B16-1,"")</f>
         <v/>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="30">
         <f>IFERROR((B28/B16)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="30">
         <f>IFERROR((B36/B16)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L16" s="16" t="n"/>
+      <c r="L16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>43738</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>3243.7</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>9.390000000000001</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3055,15 +3069,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="33">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="30">
         <f>IF(AND(D17=D13,E13&lt;&gt;""),E17/E13-1,"")</f>
         <v/>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="30">
         <f>IF(C17="","",(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,C17)+1)/2)/COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3071,28 +3085,28 @@
         <f>IF(G17="","",IF(G17&lt;=20%,"Q1 Cheapest",IF(G17&lt;=40%,"Q2",IF(G17&lt;=60%,"Q3",IF(G17&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="30">
         <f>IFERROR(B21/B17-1,"")</f>
         <v/>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="30">
         <f>IFERROR((B29/B17)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="30">
         <f>IFERROR((B37/B17)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L17" s="16" t="n"/>
+      <c r="L17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>43830</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>3226.6</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>9.81</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3100,15 +3114,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="33">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="30">
         <f>IF(AND(D18=D14,E14&lt;&gt;""),E18/E14-1,"")</f>
         <v/>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="30">
         <f>IF(C18="","",(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,C18)+1)/2)/COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3116,28 +3130,28 @@
         <f>IF(G18="","",IF(G18&lt;=20%,"Q1 Cheapest",IF(G18&lt;=40%,"Q2",IF(G18&lt;=60%,"Q3",IF(G18&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="30">
         <f>IFERROR(B22/B18-1,"")</f>
         <v/>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="30">
         <f>IFERROR((B30/B18)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="30">
         <f>IFERROR((B38/B18)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L18" s="16" t="n"/>
+      <c r="L18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>43921</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>2214.15</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>6.99</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -3145,15 +3159,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="33">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="30">
         <f>IF(AND(D19=D15,E15&lt;&gt;""),E19/E15-1,"")</f>
         <v/>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="30">
         <f>IF(C19="","",(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,C19)+1)/2)/COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3161,28 +3175,28 @@
         <f>IF(G19="","",IF(G19&lt;=20%,"Q1 Cheapest",IF(G19&lt;=40%,"Q2",IF(G19&lt;=60%,"Q3",IF(G19&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="30">
         <f>IFERROR(B23/B19-1,"")</f>
         <v/>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="30">
         <f>IFERROR((B31/B19)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="30">
         <f>IFERROR((B39/B19)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L19" s="16" t="n"/>
+      <c r="L19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44012</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>2493.95</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>9.33</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3190,15 +3204,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="33">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="30">
         <f>IF(AND(D20=D16,E16&lt;&gt;""),E20/E16-1,"")</f>
         <v/>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="30">
         <f>IF(C20="","",(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,C20)+1)/2)/COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3206,28 +3220,28 @@
         <f>IF(G20="","",IF(G20&lt;=20%,"Q1 Cheapest",IF(G20&lt;=40%,"Q2",IF(G20&lt;=60%,"Q3",IF(G20&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="30">
         <f>IFERROR(B24/B20-1,"")</f>
         <v/>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="30">
         <f>IFERROR((B32/B20)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="30">
         <f>IFERROR((B40/B20)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L20" s="16" t="n"/>
+      <c r="L20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44104</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>2260.45</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3235,15 +3249,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="33">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="30">
         <f>IF(AND(D21=D17,E17&lt;&gt;""),E21/E17-1,"")</f>
         <v/>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="30">
         <f>IF(C21="","",(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,C21)+1)/2)/COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3251,28 +3265,28 @@
         <f>IF(G21="","",IF(G21&lt;=20%,"Q1 Cheapest",IF(G21&lt;=40%,"Q2",IF(G21&lt;=60%,"Q3",IF(G21&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="30">
         <f>IFERROR(B25/B21-1,"")</f>
         <v/>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="30">
         <f>IFERROR((B33/B21)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="30">
         <f>IFERROR((B41/B21)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L21" s="16" t="n"/>
+      <c r="L21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44196</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>2797.1</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>10.65</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3280,15 +3294,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="33">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="30">
         <f>IF(AND(D22=D18,E18&lt;&gt;""),E22/E18-1,"")</f>
         <v/>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="30">
         <f>IF(C22="","",(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,C22)+1)/2)/COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3296,28 +3310,28 @@
         <f>IF(G22="","",IF(G22&lt;=20%,"Q1 Cheapest",IF(G22&lt;=40%,"Q2",IF(G22&lt;=60%,"Q3",IF(G22&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="30">
         <f>IFERROR(B26/B22-1,"")</f>
         <v/>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="30">
         <f>IFERROR((B34/B22)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="30">
         <f>IFERROR((B42/B22)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L22" s="16" t="n"/>
+      <c r="L22" s="30" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44286</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>3100.55</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>9.58</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3325,15 +3339,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="33">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="30">
         <f>IF(AND(D23=D19,E19&lt;&gt;""),E23/E19-1,"")</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="30">
         <f>IF(C23="","",(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,C23)+1)/2)/COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3341,28 +3355,28 @@
         <f>IF(G23="","",IF(G23&lt;=20%,"Q1 Cheapest",IF(G23&lt;=40%,"Q2",IF(G23&lt;=60%,"Q3",IF(G23&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="30">
         <f>IFERROR(B27/B23-1,"")</f>
         <v/>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="30">
         <f>IFERROR((B35/B23)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K23" s="16">
+      <c r="K23" s="30">
         <f>IFERROR((B43/B23)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L23" s="16" t="n"/>
+      <c r="L23" s="30" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>3609.45</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>7.35</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3370,15 +3384,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="33">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="30">
         <f>IF(AND(D24=D20,E20&lt;&gt;""),E24/E20-1,"")</f>
         <v/>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="30">
         <f>IF(C24="","",(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,C24)+1)/2)/COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3386,28 +3400,28 @@
         <f>IF(G24="","",IF(G24&lt;=20%,"Q1 Cheapest",IF(G24&lt;=40%,"Q2",IF(G24&lt;=60%,"Q3",IF(G24&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="30">
         <f>IFERROR(B28/B24-1,"")</f>
         <v/>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="30">
         <f>IFERROR((B36/B24)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K24" s="16">
+      <c r="K24" s="30">
         <f>IFERROR((B44/B24)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L24" s="16" t="n"/>
+      <c r="L24" s="30" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>4096.7</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>7.06</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3415,15 +3429,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="33">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="30">
         <f>IF(AND(D25=D21,E21&lt;&gt;""),E25/E21-1,"")</f>
         <v/>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="30">
         <f>IF(C25="","",(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,C25)+1)/2)/COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3431,25 +3445,25 @@
         <f>IF(G25="","",IF(G25&lt;=20%,"Q1 Cheapest",IF(G25&lt;=40%,"Q2",IF(G25&lt;=60%,"Q3",IF(G25&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="30">
         <f>IFERROR(B29/B25-1,"")</f>
         <v/>
       </c>
-      <c r="J25" s="16">
+      <c r="J25" s="30">
         <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="16" t="n"/>
+      <c r="K25" s="30" t="n"/>
+      <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>3835.25</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>5.91</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3457,15 +3471,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="33">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="30">
         <f>IF(AND(D26=D22,E22&lt;&gt;""),E26/E22-1,"")</f>
         <v/>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="30">
         <f>IF(C26="","",(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,C26)+1)/2)/COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3473,25 +3487,25 @@
         <f>IF(G26="","",IF(G26&lt;=20%,"Q1 Cheapest",IF(G26&lt;=40%,"Q2",IF(G26&lt;=60%,"Q3",IF(G26&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="30">
         <f>IFERROR(B30/B26-1,"")</f>
         <v/>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="30">
         <f>IFERROR((B38/B26)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="16" t="n"/>
+      <c r="K26" s="30" t="n"/>
+      <c r="L26" s="30" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>4086.25</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>5.88</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3499,15 +3513,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="33">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="30">
         <f>IF(AND(D27=D23,E23&lt;&gt;""),E27/E23-1,"")</f>
         <v/>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="30">
         <f>IF(C27="","",(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,C27)+1)/2)/COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3515,25 +3529,25 @@
         <f>IF(G27="","",IF(G27&lt;=20%,"Q1 Cheapest",IF(G27&lt;=40%,"Q2",IF(G27&lt;=60%,"Q3",IF(G27&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="30">
         <f>IFERROR(B31/B27-1,"")</f>
         <v/>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="30">
         <f>IFERROR((B39/B27)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="16" t="n"/>
+      <c r="K27" s="30" t="n"/>
+      <c r="L27" s="30" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>3819.95</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>5.56</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3541,15 +3555,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="33">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="30">
         <f>IF(AND(D28=D24,E24&lt;&gt;""),E28/E24-1,"")</f>
         <v/>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="30">
         <f>IF(C28="","",(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,C28)+1)/2)/COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3557,25 +3571,25 @@
         <f>IF(G28="","",IF(G28&lt;=20%,"Q1 Cheapest",IF(G28&lt;=40%,"Q2",IF(G28&lt;=60%,"Q3",IF(G28&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="30">
         <f>IFERROR(B32/B28-1,"")</f>
         <v/>
       </c>
-      <c r="J28" s="16">
+      <c r="J28" s="30">
         <f>IFERROR((B40/B28)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="16" t="n"/>
+      <c r="K28" s="30" t="n"/>
+      <c r="L28" s="30" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>3990.6</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>6.71</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3583,15 +3597,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="33">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="30">
         <f>IF(AND(D29=D25,E25&lt;&gt;""),E29/E25-1,"")</f>
         <v/>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="30">
         <f>IF(C29="","",(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,C29)+1)/2)/COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3599,25 +3613,25 @@
         <f>IF(G29="","",IF(G29&lt;=20%,"Q1 Cheapest",IF(G29&lt;=40%,"Q2",IF(G29&lt;=60%,"Q3",IF(G29&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="30">
         <f>IFERROR(B33/B29-1,"")</f>
         <v/>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="30">
         <f>IFERROR((B41/B29)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="16" t="n"/>
+      <c r="K29" s="30" t="n"/>
+      <c r="L29" s="30" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>4367</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>8.289999999999999</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3625,15 +3639,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="33">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="30">
         <f>IF(AND(D30=D26,E26&lt;&gt;""),E30/E26-1,"")</f>
         <v/>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="30">
         <f>IF(C30="","",(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,C30)+1)/2)/COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3641,25 +3655,25 @@
         <f>IF(G30="","",IF(G30&lt;=20%,"Q1 Cheapest",IF(G30&lt;=40%,"Q2",IF(G30&lt;=60%,"Q3",IF(G30&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="30">
         <f>IFERROR(B34/B30-1,"")</f>
         <v/>
       </c>
-      <c r="J30" s="16">
+      <c r="J30" s="30">
         <f>IFERROR((B42/B30)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="16" t="n"/>
+      <c r="K30" s="30" t="n"/>
+      <c r="L30" s="30" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>4474</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>8.56</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3667,15 +3681,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="33">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="30">
         <f>IF(AND(D31=D27,E27&lt;&gt;""),E31/E27-1,"")</f>
         <v/>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="30">
         <f>IF(C31="","",(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,C31)+1)/2)/COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3683,25 +3697,25 @@
         <f>IF(G31="","",IF(G31&lt;=20%,"Q1 Cheapest",IF(G31&lt;=40%,"Q2",IF(G31&lt;=60%,"Q3",IF(G31&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="30">
         <f>IFERROR(B35/B31-1,"")</f>
         <v/>
       </c>
-      <c r="J31" s="16">
+      <c r="J31" s="30">
         <f>IFERROR((B43/B31)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K31" s="16" t="n"/>
-      <c r="L31" s="16" t="n"/>
+      <c r="K31" s="30" t="n"/>
+      <c r="L31" s="30" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>5081.6</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>9.550000000000001</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3709,15 +3723,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="33">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="30">
         <f>IF(AND(D32=D28,E28&lt;&gt;""),E32/E28-1,"")</f>
         <v/>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="30">
         <f>IF(C32="","",(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,C32)+1)/2)/COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3725,25 +3739,25 @@
         <f>IF(G32="","",IF(G32&lt;=20%,"Q1 Cheapest",IF(G32&lt;=40%,"Q2",IF(G32&lt;=60%,"Q3",IF(G32&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="30">
         <f>IFERROR(B36/B32-1,"")</f>
         <v/>
       </c>
-      <c r="J32" s="16">
+      <c r="J32" s="30">
         <f>IFERROR((B44/B32)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K32" s="16" t="n"/>
-      <c r="L32" s="16" t="n"/>
+      <c r="K32" s="30" t="n"/>
+      <c r="L32" s="30" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>5991.75</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>8.57</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3751,15 +3765,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="33">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="30">
         <f>IF(AND(D33=D29,E29&lt;&gt;""),E33/E29-1,"")</f>
         <v/>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="30">
         <f>IF(C33="","",(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,C33)+1)/2)/COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3767,22 +3781,22 @@
         <f>IF(G33="","",IF(G33&lt;=20%,"Q1 Cheapest",IF(G33&lt;=40%,"Q2",IF(G33&lt;=60%,"Q3",IF(G33&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="30">
         <f>IFERROR(B37/B33-1,"")</f>
         <v/>
       </c>
-      <c r="J33" s="16" t="n"/>
-      <c r="K33" s="16" t="n"/>
-      <c r="L33" s="16" t="n"/>
+      <c r="J33" s="30" t="n"/>
+      <c r="K33" s="30" t="n"/>
+      <c r="L33" s="30" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>7854.95</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>9.33</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3790,15 +3804,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="33">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="30">
         <f>IF(AND(D34=D30,E30&lt;&gt;""),E34/E30-1,"")</f>
         <v/>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="30">
         <f>IF(C34="","",(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,C34)+1)/2)/COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3806,22 +3820,22 @@
         <f>IF(G34="","",IF(G34&lt;=20%,"Q1 Cheapest",IF(G34&lt;=40%,"Q2",IF(G34&lt;=60%,"Q3",IF(G34&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I34" s="16">
+      <c r="I34" s="30">
         <f>IFERROR(B38/B34-1,"")</f>
         <v/>
       </c>
-      <c r="J34" s="16" t="n"/>
-      <c r="K34" s="16" t="n"/>
-      <c r="L34" s="16" t="n"/>
+      <c r="J34" s="30" t="n"/>
+      <c r="K34" s="30" t="n"/>
+      <c r="L34" s="30" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>9122.15</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>10.27</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3829,15 +3843,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="33">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="30">
         <f>IF(AND(D35=D31,E31&lt;&gt;""),E35/E31-1,"")</f>
         <v/>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="30">
         <f>IF(C35="","",(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,C35)+1)/2)/COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3845,22 +3859,22 @@
         <f>IF(G35="","",IF(G35&lt;=20%,"Q1 Cheapest",IF(G35&lt;=40%,"Q2",IF(G35&lt;=60%,"Q3",IF(G35&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I35" s="16">
+      <c r="I35" s="30">
         <f>IFERROR(B39/B35-1,"")</f>
         <v/>
       </c>
-      <c r="J35" s="16" t="n"/>
-      <c r="K35" s="16" t="n"/>
-      <c r="L35" s="16" t="n"/>
+      <c r="J35" s="30" t="n"/>
+      <c r="K35" s="30" t="n"/>
+      <c r="L35" s="30" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>10685.5</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>11.66</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3868,15 +3882,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="33">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="30">
         <f>IF(AND(D36=D32,E32&lt;&gt;""),E36/E32-1,"")</f>
         <v/>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="30">
         <f>IF(C36="","",(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,C36)+1)/2)/COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3884,22 +3898,22 @@
         <f>IF(G36="","",IF(G36&lt;=20%,"Q1 Cheapest",IF(G36&lt;=40%,"Q2",IF(G36&lt;=60%,"Q3",IF(G36&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I36" s="16">
+      <c r="I36" s="30">
         <f>IFERROR(B40/B36-1,"")</f>
         <v/>
       </c>
-      <c r="J36" s="16" t="n"/>
-      <c r="K36" s="16" t="n"/>
-      <c r="L36" s="16" t="n"/>
+      <c r="J36" s="30" t="n"/>
+      <c r="K36" s="30" t="n"/>
+      <c r="L36" s="30" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>11286</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>13.31</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3907,15 +3921,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E37" s="21">
+      <c r="E37" s="33">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="30">
         <f>IF(AND(D37=D33,E33&lt;&gt;""),E37/E33-1,"")</f>
         <v/>
       </c>
-      <c r="G37" s="16">
+      <c r="G37" s="30">
         <f>IF(C37="","",(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,C37)+1)/2)/COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3923,22 +3937,22 @@
         <f>IF(G37="","",IF(G37&lt;=20%,"Q1 Cheapest",IF(G37&lt;=40%,"Q2",IF(G37&lt;=60%,"Q3",IF(G37&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I37" s="16">
+      <c r="I37" s="30">
         <f>IFERROR(B41/B37-1,"")</f>
         <v/>
       </c>
-      <c r="J37" s="16" t="n"/>
-      <c r="K37" s="16" t="n"/>
-      <c r="L37" s="16" t="n"/>
+      <c r="J37" s="30" t="n"/>
+      <c r="K37" s="30" t="n"/>
+      <c r="L37" s="30" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>9532.200000000001</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>12.35</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3946,15 +3960,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E38" s="21">
+      <c r="E38" s="33">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="30">
         <f>IF(AND(D38=D34,E34&lt;&gt;""),E38/E34-1,"")</f>
         <v/>
       </c>
-      <c r="G38" s="16">
+      <c r="G38" s="30">
         <f>IF(C38="","",(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,C38)+1)/2)/COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3962,22 +3976,22 @@
         <f>IF(G38="","",IF(G38&lt;=20%,"Q1 Cheapest",IF(G38&lt;=40%,"Q2",IF(G38&lt;=60%,"Q3",IF(G38&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I38" s="16">
+      <c r="I38" s="30">
         <f>IFERROR(B42/B38-1,"")</f>
         <v/>
       </c>
-      <c r="J38" s="16" t="n"/>
-      <c r="K38" s="16" t="n"/>
-      <c r="L38" s="16" t="n"/>
+      <c r="J38" s="30" t="n"/>
+      <c r="K38" s="30" t="n"/>
+      <c r="L38" s="30" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>9342.700000000001</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>12.17</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3985,15 +3999,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E39" s="21">
+      <c r="E39" s="33">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
-      <c r="F39" s="16">
+      <c r="F39" s="30">
         <f>IF(AND(D39=D35,E35&lt;&gt;""),E39/E35-1,"")</f>
         <v/>
       </c>
-      <c r="G39" s="16">
+      <c r="G39" s="30">
         <f>IF(C39="","",(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,C39)+1)/2)/COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4001,22 +4015,22 @@
         <f>IF(G39="","",IF(G39&lt;=20%,"Q1 Cheapest",IF(G39&lt;=40%,"Q2",IF(G39&lt;=60%,"Q3",IF(G39&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I39" s="16">
+      <c r="I39" s="30">
         <f>IFERROR(B43/B39-1,"")</f>
         <v/>
       </c>
-      <c r="J39" s="16" t="n"/>
-      <c r="K39" s="16" t="n"/>
-      <c r="L39" s="16" t="n"/>
+      <c r="J39" s="30" t="n"/>
+      <c r="K39" s="30" t="n"/>
+      <c r="L39" s="30" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>10093.65</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>12.94</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -4024,15 +4038,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E40" s="21">
+      <c r="E40" s="33">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="30">
         <f>IF(AND(D40=D36,E36&lt;&gt;""),E40/E36-1,"")</f>
         <v/>
       </c>
-      <c r="G40" s="16">
+      <c r="G40" s="30">
         <f>IF(C40="","",(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,C40)+1)/2)/COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4040,22 +4054,22 @@
         <f>IF(G40="","",IF(G40&lt;=20%,"Q1 Cheapest",IF(G40&lt;=40%,"Q2",IF(G40&lt;=60%,"Q3",IF(G40&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I40" s="16">
+      <c r="I40" s="30">
         <f>IFERROR(B44/B40-1,"")</f>
         <v/>
       </c>
-      <c r="J40" s="16" t="n"/>
-      <c r="K40" s="16" t="n"/>
-      <c r="L40" s="16" t="n"/>
+      <c r="J40" s="30" t="n"/>
+      <c r="K40" s="30" t="n"/>
+      <c r="L40" s="30" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>9800.85</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>11.93</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -4063,15 +4077,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E41" s="21">
+      <c r="E41" s="33">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
-      <c r="F41" s="16">
+      <c r="F41" s="30">
         <f>IF(AND(D41=D37,E37&lt;&gt;""),E41/E37-1,"")</f>
         <v/>
       </c>
-      <c r="G41" s="16">
+      <c r="G41" s="30">
         <f>IF(C41="","",(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,C41)+1)/2)/COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4079,19 +4093,19 @@
         <f>IF(G41="","",IF(G41&lt;=20%,"Q1 Cheapest",IF(G41&lt;=40%,"Q2",IF(G41&lt;=60%,"Q3",IF(G41&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I41" s="16" t="n"/>
-      <c r="J41" s="16" t="n"/>
-      <c r="K41" s="16" t="n"/>
-      <c r="L41" s="16" t="n"/>
+      <c r="I41" s="30" t="n"/>
+      <c r="J41" s="30" t="n"/>
+      <c r="K41" s="30" t="n"/>
+      <c r="L41" s="30" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>9853.65</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>11.23</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -4099,15 +4113,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E42" s="21">
+      <c r="E42" s="33">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="30">
         <f>IF(AND(D42=D38,E38&lt;&gt;""),E42/E38-1,"")</f>
         <v/>
       </c>
-      <c r="G42" s="16">
+      <c r="G42" s="30">
         <f>IF(C42="","",(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,C42)+1)/2)/COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4115,19 +4129,19 @@
         <f>IF(G42="","",IF(G42&lt;=20%,"Q1 Cheapest",IF(G42&lt;=40%,"Q2",IF(G42&lt;=60%,"Q3",IF(G42&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I42" s="16" t="n"/>
-      <c r="J42" s="16" t="n"/>
-      <c r="K42" s="16" t="n"/>
-      <c r="L42" s="16" t="n"/>
+      <c r="I42" s="30" t="n"/>
+      <c r="J42" s="30" t="n"/>
+      <c r="K42" s="30" t="n"/>
+      <c r="L42" s="30" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>9559</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>10.35</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -4135,15 +4149,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E43" s="21">
+      <c r="E43" s="33">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
-      <c r="F43" s="16">
+      <c r="F43" s="30">
         <f>IF(AND(D43=D39,E39&lt;&gt;""),E43/E39-1,"")</f>
         <v/>
       </c>
-      <c r="G43" s="16">
+      <c r="G43" s="30">
         <f>IF(C43="","",(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,C43)+1)/2)/COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4151,19 +4165,19 @@
         <f>IF(G43="","",IF(G43&lt;=20%,"Q1 Cheapest",IF(G43&lt;=40%,"Q2",IF(G43&lt;=60%,"Q3",IF(G43&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I43" s="16" t="n"/>
-      <c r="J43" s="16" t="n"/>
-      <c r="K43" s="16" t="n"/>
-      <c r="L43" s="16" t="n"/>
+      <c r="I43" s="30" t="n"/>
+      <c r="J43" s="30" t="n"/>
+      <c r="K43" s="30" t="n"/>
+      <c r="L43" s="30" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>9980.700000000001</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>10.16</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4171,15 +4185,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E44" s="21">
+      <c r="E44" s="33">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
-      <c r="F44" s="16">
+      <c r="F44" s="30">
         <f>IF(AND(D44=D40,E40&lt;&gt;""),E44/E40-1,"")</f>
         <v/>
       </c>
-      <c r="G44" s="16">
+      <c r="G44" s="30">
         <f>IF(C44="","",(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,C44)+1)/2)/COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4187,10 +4201,10 @@
         <f>IF(G44="","",IF(G44&lt;=20%,"Q1 Cheapest",IF(G44&lt;=40%,"Q2",IF(G44&lt;=60%,"Q3",IF(G44&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I44" s="16" t="n"/>
-      <c r="J44" s="16" t="n"/>
-      <c r="K44" s="16" t="n"/>
-      <c r="L44" s="16" t="n"/>
+      <c r="I44" s="30" t="n"/>
+      <c r="J44" s="30" t="n"/>
+      <c r="K44" s="30" t="n"/>
+      <c r="L44" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4267,30 +4281,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>46283</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>9597</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>10.89</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="26" t="n">
         <v>0.613636363636</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="26" t="n">
         <v>0.07295218549430001</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="34">
         <f>IF(D2="","",100*(1-D2))</f>
         <v/>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="34">
         <f>IF(E2="","",IF(E2&lt;=0,20,IF(E2&lt;5%,20+400*E2,IF(E2&lt;10%,40+400*(E2-5%),IF(E2&lt;15%,60+400*(E2-10%),IF(E2&lt;25%,80+200*(E2-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="34">
         <f>IF(OR(F2="",G2=""),"",70%*F2+30%*G2)</f>
         <v/>
       </c>
@@ -4300,30 +4314,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>46286</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>9604</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>10.9</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="26" t="n">
         <v>0.613636363636</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="26" t="n">
         <v>0.0730490359553</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="34">
         <f>IF(D3="","",100*(1-D3))</f>
         <v/>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="34">
         <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="34">
         <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
         <v/>
       </c>
@@ -4333,30 +4347,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>46287</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>9616.700000000001</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>10.91</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="26" t="n">
         <v>0.613636363636</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="26" t="n">
         <v>0.0730037794471</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="34">
         <f>IF(D4="","",100*(1-D4))</f>
         <v/>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="34">
         <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="34">
         <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
         <v/>
       </c>
@@ -4476,4 +4490,43 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>Nifty Pse Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Official composition data is not currently available for this index.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Monthly PE History" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Composition" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sources &amp; Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -110,7 +110,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -153,6 +153,9 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4389,6 +4392,512 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>NIFTY Pse Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As of</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Retrieved 2026-09-23</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Weight coverage</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>NSE Indices — Index Constituent CSV</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 weight</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>Sector / Industry</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bharat Electronics Ltd.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bharat Heavy Electricals Ltd.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bharat Petroleum Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BPCL</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Coal India Ltd.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Container Corporation of India Ltd.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GAIL (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Hindustan Aeronautics Ltd.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Hindustan Petroleum Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HINDPETRO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Indian Oil Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Indian Railway Catering And Tourism Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Indian Railway Finance Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>IRFC</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NHPC Ltd.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NMDC Ltd.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NMDC</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NTPC Ltd.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Oil &amp; Natural Gas Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Oil India Ltd.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Power Finance Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Power Grid Corporation of India Ltd.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Rail Vikas Nigam Ltd.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>RVNL</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>REC Ltd.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
@@ -4490,43 +4999,4 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="35" t="inlineStr">
-        <is>
-          <t>Nifty Pse Composition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Official composition data is not currently available for this index.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9616.700000000001</v>
+        <v>9637.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>10.91</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>881.4573785517874</v>
+        <v>880.9506398537478</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07300377944707193</v>
+        <v>0.0726146406503998</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.09165902841429881</v>
+        <v>0.09140767824497258</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>49.20151177882877</v>
+        <v>49.04585626015992</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>41.80590807910318</v>
+        <v>41.75921142350252</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.157674896651253</v>
+        <v>7.152905166829186</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6309.185350928149</v>
+        <v>6301.35638353135</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.3439344732675296</v>
+        <v>-0.3461695459936759</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>11.06632782812451</v>
+        <v>11.06199171010445</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9754.49631757333</v>
+        <v>9745.068675073373</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.01432885684001062</v>
+        <v>0.01115097898578199</v>
       </c>
     </row>
     <row r="16">
@@ -4222,7 +4222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4379,6 +4379,39 @@
       </c>
       <c r="I4">
         <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <v>9637.6</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>0.613636363636</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>0.07261464065040001</v>
+      </c>
+      <c r="F5" s="34">
+        <f>IF(D5="","",100*(1-D5))</f>
+        <v/>
+      </c>
+      <c r="G5" s="34">
+        <f>IF(E5="","",IF(E5&lt;=0,20,IF(E5&lt;5%,20+400*E5,IF(E5&lt;10%,40+400*(E5-5%),IF(E5&lt;15%,60+400*(E5-10%),IF(E5&lt;25%,80+200*(E5-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H5" s="34">
+        <f>IF(OR(F5="",G5=""),"",70%*F5+30%*G5)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9637.6</v>
+        <v>9555.450000000001</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>10.94</v>
+        <v>10.84</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>880.9506398537478</v>
+        <v>881.499077490775</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.0726146406503998</v>
+        <v>0.07345137443367999</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.09140767824497258</v>
+        <v>0.09225092250922509</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>49.04585626015992</v>
+        <v>49.380549773472</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>41.75921142350252</v>
+        <v>41.85961947749614</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.152905166829186</v>
+        <v>7.16316113234425</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6301.35638353135</v>
+        <v>6314.319930079231</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.3461695459936759</v>
+        <v>-0.3391917774590175</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>11.06199171010445</v>
+        <v>11.07131531511815</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9745.068675073373</v>
+        <v>9759.354236886136</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.01115097898578199</v>
+        <v>0.02133905121016122</v>
       </c>
     </row>
     <row r="16">
@@ -4222,7 +4222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4412,6 +4412,39 @@
       </c>
       <c r="I5">
         <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>9555.450000000001</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.613636363636</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0.07345137443370001</v>
+      </c>
+      <c r="F6" s="34">
+        <f>IF(D6="","",100*(1-D6))</f>
+        <v/>
+      </c>
+      <c r="G6" s="34">
+        <f>IF(E6="","",IF(E6&lt;=0,20,IF(E6&lt;5%,20+400*E6,IF(E6&lt;10%,40+400*(E6-5%),IF(E6&lt;15%,60+400*(E6-10%),IF(E6&lt;25%,80+200*(E6-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H6" s="34">
+        <f>IF(OR(F6="",G6=""),"",70%*F6+30%*G6)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4452,7 +4485,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-23</t>
+          <t>Retrieved 2026-09-24</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9555.450000000001</v>
+        <v>9572.85</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>10.84</v>
+        <v>10.86</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>881.499077490775</v>
+        <v>881.4779005524863</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07345137443367999</v>
+        <v>0.07347816883577507</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.09225092250922509</v>
+        <v>0.09208103130755065</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>49.380549773472</v>
+        <v>49.39126753431002</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>41.85961947749614</v>
+        <v>41.86283480574755</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.16316113234425</v>
+        <v>7.1634895551585</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6314.319930079231</v>
+        <v>6314.457733710778</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.3391917774590175</v>
+        <v>-0.3403784940001381</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>11.07131531511815</v>
+        <v>11.07161388131292</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9759.354236886136</v>
+        <v>9759.382959827477</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.02133905121016122</v>
+        <v>0.01948562443028745</v>
       </c>
     </row>
     <row r="16">
@@ -4222,7 +4222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4445,6 +4445,39 @@
       </c>
       <c r="I6">
         <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>9572.85</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>0.613636363636</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>0.0734781688358</v>
+      </c>
+      <c r="F7" s="34">
+        <f>IF(D7="","",100*(1-D7))</f>
+        <v/>
+      </c>
+      <c r="G7" s="34">
+        <f>IF(E7="","",IF(E7&lt;=0,20,IF(E7&lt;5%,20+400*E7,IF(E7&lt;10%,40+400*(E7-5%),IF(E7&lt;15%,60+400*(E7-10%),IF(E7&lt;25%,80+200*(E7-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H7" s="34">
+        <f>IF(OR(F7="",G7=""),"",70%*F7+30%*G7)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4485,7 +4518,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-24</t>
+          <t>Retrieved 2026-09-25</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9572.85</v>
+        <v>9390.299999999999</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>10.86</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>881.4779005524863</v>
+        <v>880.8911819887429</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07347816883577507</v>
+        <v>0.07241701909341502</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.09208103130755065</v>
+        <v>0.09380863039399624</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>49.39126753431002</v>
+        <v>48.96680763736601</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>41.86283480574755</v>
+        <v>41.73549683666435</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.1634895551585</v>
+        <v>7.150482891173573</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6314.457733710778</v>
+        <v>6298.797325796173</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.3403784940001381</v>
+        <v>-0.3292229933233045</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>11.07161388131292</v>
+        <v>11.05978964132662</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9759.382959827477</v>
+        <v>9742.471169695065</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.01948562443028745</v>
+        <v>0.03750371869855762</v>
       </c>
     </row>
     <row r="16">
@@ -4222,7 +4222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4478,6 +4478,39 @@
       </c>
       <c r="I7">
         <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>9390.299999999999</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>0.613636363636</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>0.0724170190934</v>
+      </c>
+      <c r="F8" s="34">
+        <f>IF(D8="","",100*(1-D8))</f>
+        <v/>
+      </c>
+      <c r="G8" s="34">
+        <f>IF(E8="","",IF(E8&lt;=0,20,IF(E8&lt;5%,20+400*E8,IF(E8&lt;10%,40+400*(E8-5%),IF(E8&lt;15%,60+400*(E8-10%),IF(E8&lt;25%,80+200*(E8-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H8" s="34">
+        <f>IF(OR(F8="",G8=""),"",70%*F8+30%*G8)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4518,7 +4551,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-25</t>
+          <t>Retrieved 2026-09-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9390.299999999999</v>
+        <v>9343.700000000001</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>10.66</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>880.8911819887429</v>
+        <v>881.4811320754718</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07241701909341502</v>
+        <v>0.07331608923454325</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.09380863039399624</v>
+        <v>0.09433962264150944</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>48.96680763736601</v>
+        <v>49.3264356938173</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>41.73549683666435</v>
+        <v>41.84338525359973</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.150482891173573</v>
+        <v>7.161502922331973</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6298.797325796173</v>
+        <v>6312.729703338987</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.3292229933233045</v>
+        <v>-0.3243865167611346</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>11.05978964132662</v>
+        <v>11.06980785147062</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9742.471169695065</v>
+        <v>9757.826756772272</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.03750371869855762</v>
+        <v>0.04432149542175701</v>
       </c>
     </row>
     <row r="16">
@@ -4222,7 +4222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4511,6 +4511,39 @@
       </c>
       <c r="I8">
         <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>9343.700000000001</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>0.613636363636</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>0.0733160892345</v>
+      </c>
+      <c r="F9" s="34">
+        <f>IF(D9="","",100*(1-D9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="34">
+        <f>IF(E9="","",IF(E9&lt;=0,20,IF(E9&lt;5%,20+400*E9,IF(E9&lt;10%,40+400*(E9-5%),IF(E9&lt;15%,60+400*(E9-10%),IF(E9&lt;25%,80+200*(E9-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H9" s="34">
+        <f>IF(OR(F9="",G9=""),"",70%*F9+30%*G9)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4530,8 +4563,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
@@ -4551,7 +4584,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-28</t>
+          <t>Retrieved 2026-09-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -4801,17 +4834,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Indian Railway Catering And Tourism Corporation Ltd.</t>
+          <t>Indian Railway Finance Corporation Ltd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4821,17 +4854,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Indian Railway Finance Corporation Ltd.</t>
+          <t>National Aluminium Co. Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -4981,17 +5014,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rail Vikas Nigam Ltd.</t>
+          <t>REC Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RVNL</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5001,17 +5034,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>REC Ltd.</t>
+          <t>Steel Authority of India Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9343.700000000001</v>
+        <v>9360.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>10.6</v>
+        <v>10.54</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6136363636363636</v>
+        <v>0.5970149253731343</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>881.4811320754718</v>
+        <v>888.0834914611006</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07331608923454325</v>
+        <v>0.08101195846594234</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.09433962264150944</v>
+        <v>0.09487666034155598</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>38.63636363636363</v>
+        <v>40.29850746268657</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>49.3264356938173</v>
+        <v>52.40478338637693</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>41.84338525359973</v>
+        <v>43.93039023979368</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.161502922331973</v>
+        <v>7.272306730071805</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6312.729703338987</v>
+        <v>6458.415551818229</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.3243865167611346</v>
+        <v>-0.3100278244713657</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>11.06980785147062</v>
+        <v>11.11435126345729</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9757.826756772272</v>
+        <v>9870.471875376246</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.04432149542175701</v>
+        <v>0.05449252973978114</v>
       </c>
     </row>
     <row r="16">
@@ -835,16 +835,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" s="30" t="n">
-        <v>0.214735699669954</v>
+        <v>0.371152264845733</v>
       </c>
       <c r="D19" s="30" t="n">
-        <v>0.299789514883279</v>
+        <v>0.2879692484943599</v>
       </c>
       <c r="E19" s="30" t="n">
-        <v>0.2255865728794684</v>
+        <v>0.2043214210656309</v>
       </c>
       <c r="F19" s="30" t="n">
         <v>0.1287781696551022</v>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" s="30" t="n">
-        <v>0.1251624476057706</v>
+        <v>0.03679711973238464</v>
       </c>
       <c r="D20" s="30" t="n">
         <v>0.0462515327216334</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" s="30" t="n">
         <v>-0.01560536424732312</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="C22" s="30" t="n">
-        <v>-0.01119020374195645</v>
+        <v>-0.02612528304530704</v>
       </c>
       <c r="D22" s="30" t="n">
         <v>-0.1337621850380084</v>
@@ -919,7 +919,9 @@
       <c r="E22" s="30" t="n">
         <v>0.003776895891633769</v>
       </c>
-      <c r="F22" s="30" t="n"/>
+      <c r="F22" s="30" t="n">
+        <v>0.1034494099301289</v>
+      </c>
       <c r="G22" s="30" t="n">
         <v>1</v>
       </c>
@@ -938,7 +940,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
@@ -948,7 +950,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27">
@@ -971,7 +973,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2290,6 +2292,25 @@
       </c>
       <c r="E66" s="20">
         <f>IFERROR(1/C66,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B67" s="24" t="n">
+        <v>9360.4</v>
+      </c>
+      <c r="C67" s="25" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="D67" s="32">
+        <f>IFERROR(B67/C67,"")</f>
+        <v/>
+      </c>
+      <c r="E67" s="20">
+        <f>IFERROR(1/C67,"")</f>
         <v/>
       </c>
     </row>
@@ -2306,7 +2327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2406,7 +2427,7 @@
       </c>
       <c r="F2" s="30" t="n"/>
       <c r="G2" s="30">
-        <f>IF(C2="","",(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,C2)+1)/2)/COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C2="","",(COUNTIFS($D$2:$D$45,D2,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$45,D2,$C$2:$C$45,C2)+1)/2)/COUNTIFS($D$2:$D$45,D2,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H2">
@@ -2451,7 +2472,7 @@
       </c>
       <c r="F3" s="30" t="n"/>
       <c r="G3" s="30">
-        <f>IF(C3="","",(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,C3)+1)/2)/COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C3="","",(COUNTIFS($D$2:$D$45,D3,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$45,D3,$C$2:$C$45,C3)+1)/2)/COUNTIFS($D$2:$D$45,D3,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H3">
@@ -2496,7 +2517,7 @@
       </c>
       <c r="F4" s="30" t="n"/>
       <c r="G4" s="30">
-        <f>IF(C4="","",(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,C4)+1)/2)/COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C4="","",(COUNTIFS($D$2:$D$45,D4,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$45,D4,$C$2:$C$45,C4)+1)/2)/COUNTIFS($D$2:$D$45,D4,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H4">
@@ -2541,7 +2562,7 @@
       </c>
       <c r="F5" s="30" t="n"/>
       <c r="G5" s="30">
-        <f>IF(C5="","",(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,C5)+1)/2)/COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C5="","",(COUNTIFS($D$2:$D$45,D5,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$45,D5,$C$2:$C$45,C5)+1)/2)/COUNTIFS($D$2:$D$45,D5,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H5">
@@ -2560,7 +2581,10 @@
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="30" t="n"/>
+      <c r="L5" s="30">
+        <f>IFERROR((B45/B5)^(1/10)-1,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="31" t="n">
@@ -2586,7 +2610,7 @@
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>IF(C6="","",(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,C6)+1)/2)/COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C6="","",(COUNTIFS($D$2:$D$45,D6,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$45,D6,$C$2:$C$45,C6)+1)/2)/COUNTIFS($D$2:$D$45,D6,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H6">
@@ -2631,7 +2655,7 @@
         <v/>
       </c>
       <c r="G7" s="30">
-        <f>IF(C7="","",(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,C7)+1)/2)/COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C7="","",(COUNTIFS($D$2:$D$45,D7,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$45,D7,$C$2:$C$45,C7)+1)/2)/COUNTIFS($D$2:$D$45,D7,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H7">
@@ -2676,7 +2700,7 @@
         <v/>
       </c>
       <c r="G8" s="30">
-        <f>IF(C8="","",(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,C8)+1)/2)/COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C8="","",(COUNTIFS($D$2:$D$45,D8,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$45,D8,$C$2:$C$45,C8)+1)/2)/COUNTIFS($D$2:$D$45,D8,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H8">
@@ -2721,7 +2745,7 @@
         <v/>
       </c>
       <c r="G9" s="30">
-        <f>IF(C9="","",(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,C9)+1)/2)/COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C9="","",(COUNTIFS($D$2:$D$45,D9,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$45,D9,$C$2:$C$45,C9)+1)/2)/COUNTIFS($D$2:$D$45,D9,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H9">
@@ -2766,7 +2790,7 @@
         <v/>
       </c>
       <c r="G10" s="30">
-        <f>IF(C10="","",(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,C10)+1)/2)/COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C10="","",(COUNTIFS($D$2:$D$45,D10,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$45,D10,$C$2:$C$45,C10)+1)/2)/COUNTIFS($D$2:$D$45,D10,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H10">
@@ -2811,7 +2835,7 @@
         <v/>
       </c>
       <c r="G11" s="30">
-        <f>IF(C11="","",(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,C11)+1)/2)/COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C11="","",(COUNTIFS($D$2:$D$45,D11,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$45,D11,$C$2:$C$45,C11)+1)/2)/COUNTIFS($D$2:$D$45,D11,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H11">
@@ -2856,7 +2880,7 @@
         <v/>
       </c>
       <c r="G12" s="30">
-        <f>IF(C12="","",(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,C12)+1)/2)/COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C12="","",(COUNTIFS($D$2:$D$45,D12,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$45,D12,$C$2:$C$45,C12)+1)/2)/COUNTIFS($D$2:$D$45,D12,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H12">
@@ -2901,7 +2925,7 @@
         <v/>
       </c>
       <c r="G13" s="30">
-        <f>IF(C13="","",(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,C13)+1)/2)/COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C13="","",(COUNTIFS($D$2:$D$45,D13,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$45,D13,$C$2:$C$45,C13)+1)/2)/COUNTIFS($D$2:$D$45,D13,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H13">
@@ -2946,7 +2970,7 @@
         <v/>
       </c>
       <c r="G14" s="30">
-        <f>IF(C14="","",(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,C14)+1)/2)/COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C14="","",(COUNTIFS($D$2:$D$45,D14,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$45,D14,$C$2:$C$45,C14)+1)/2)/COUNTIFS($D$2:$D$45,D14,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H14">
@@ -2991,7 +3015,7 @@
         <v/>
       </c>
       <c r="G15" s="30">
-        <f>IF(C15="","",(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,C15)+1)/2)/COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C15="","",(COUNTIFS($D$2:$D$45,D15,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$45,D15,$C$2:$C$45,C15)+1)/2)/COUNTIFS($D$2:$D$45,D15,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H15">
@@ -3036,7 +3060,7 @@
         <v/>
       </c>
       <c r="G16" s="30">
-        <f>IF(C16="","",(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,C16)+1)/2)/COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C16="","",(COUNTIFS($D$2:$D$45,D16,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$45,D16,$C$2:$C$45,C16)+1)/2)/COUNTIFS($D$2:$D$45,D16,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H16">
@@ -3081,7 +3105,7 @@
         <v/>
       </c>
       <c r="G17" s="30">
-        <f>IF(C17="","",(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,C17)+1)/2)/COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C17="","",(COUNTIFS($D$2:$D$45,D17,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$45,D17,$C$2:$C$45,C17)+1)/2)/COUNTIFS($D$2:$D$45,D17,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H17">
@@ -3126,7 +3150,7 @@
         <v/>
       </c>
       <c r="G18" s="30">
-        <f>IF(C18="","",(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,C18)+1)/2)/COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C18="","",(COUNTIFS($D$2:$D$45,D18,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$45,D18,$C$2:$C$45,C18)+1)/2)/COUNTIFS($D$2:$D$45,D18,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H18">
@@ -3171,7 +3195,7 @@
         <v/>
       </c>
       <c r="G19" s="30">
-        <f>IF(C19="","",(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,C19)+1)/2)/COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C19="","",(COUNTIFS($D$2:$D$45,D19,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$45,D19,$C$2:$C$45,C19)+1)/2)/COUNTIFS($D$2:$D$45,D19,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H19">
@@ -3216,7 +3240,7 @@
         <v/>
       </c>
       <c r="G20" s="30">
-        <f>IF(C20="","",(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,C20)+1)/2)/COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C20="","",(COUNTIFS($D$2:$D$45,D20,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$45,D20,$C$2:$C$45,C20)+1)/2)/COUNTIFS($D$2:$D$45,D20,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H20">
@@ -3261,7 +3285,7 @@
         <v/>
       </c>
       <c r="G21" s="30">
-        <f>IF(C21="","",(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,C21)+1)/2)/COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C21="","",(COUNTIFS($D$2:$D$45,D21,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$45,D21,$C$2:$C$45,C21)+1)/2)/COUNTIFS($D$2:$D$45,D21,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H21">
@@ -3306,7 +3330,7 @@
         <v/>
       </c>
       <c r="G22" s="30">
-        <f>IF(C22="","",(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,C22)+1)/2)/COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C22="","",(COUNTIFS($D$2:$D$45,D22,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$45,D22,$C$2:$C$45,C22)+1)/2)/COUNTIFS($D$2:$D$45,D22,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H22">
@@ -3351,7 +3375,7 @@
         <v/>
       </c>
       <c r="G23" s="30">
-        <f>IF(C23="","",(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,C23)+1)/2)/COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C23="","",(COUNTIFS($D$2:$D$45,D23,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$45,D23,$C$2:$C$45,C23)+1)/2)/COUNTIFS($D$2:$D$45,D23,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H23">
@@ -3396,7 +3420,7 @@
         <v/>
       </c>
       <c r="G24" s="30">
-        <f>IF(C24="","",(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,C24)+1)/2)/COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C24="","",(COUNTIFS($D$2:$D$45,D24,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$45,D24,$C$2:$C$45,C24)+1)/2)/COUNTIFS($D$2:$D$45,D24,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H24">
@@ -3441,7 +3465,7 @@
         <v/>
       </c>
       <c r="G25" s="30">
-        <f>IF(C25="","",(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,C25)+1)/2)/COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C25="","",(COUNTIFS($D$2:$D$45,D25,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$45,D25,$C$2:$C$45,C25)+1)/2)/COUNTIFS($D$2:$D$45,D25,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H25">
@@ -3456,7 +3480,10 @@
         <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K25" s="30" t="n"/>
+      <c r="K25" s="30">
+        <f>IFERROR((B45/B25)^(1/5)-1,"")</f>
+        <v/>
+      </c>
       <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
@@ -3483,7 +3510,7 @@
         <v/>
       </c>
       <c r="G26" s="30">
-        <f>IF(C26="","",(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,C26)+1)/2)/COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C26="","",(COUNTIFS($D$2:$D$45,D26,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$45,D26,$C$2:$C$45,C26)+1)/2)/COUNTIFS($D$2:$D$45,D26,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H26">
@@ -3525,7 +3552,7 @@
         <v/>
       </c>
       <c r="G27" s="30">
-        <f>IF(C27="","",(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,C27)+1)/2)/COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C27="","",(COUNTIFS($D$2:$D$45,D27,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$45,D27,$C$2:$C$45,C27)+1)/2)/COUNTIFS($D$2:$D$45,D27,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H27">
@@ -3567,7 +3594,7 @@
         <v/>
       </c>
       <c r="G28" s="30">
-        <f>IF(C28="","",(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,C28)+1)/2)/COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C28="","",(COUNTIFS($D$2:$D$45,D28,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$45,D28,$C$2:$C$45,C28)+1)/2)/COUNTIFS($D$2:$D$45,D28,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H28">
@@ -3609,7 +3636,7 @@
         <v/>
       </c>
       <c r="G29" s="30">
-        <f>IF(C29="","",(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,C29)+1)/2)/COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C29="","",(COUNTIFS($D$2:$D$45,D29,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$45,D29,$C$2:$C$45,C29)+1)/2)/COUNTIFS($D$2:$D$45,D29,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H29">
@@ -3651,7 +3678,7 @@
         <v/>
       </c>
       <c r="G30" s="30">
-        <f>IF(C30="","",(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,C30)+1)/2)/COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C30="","",(COUNTIFS($D$2:$D$45,D30,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$45,D30,$C$2:$C$45,C30)+1)/2)/COUNTIFS($D$2:$D$45,D30,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H30">
@@ -3693,7 +3720,7 @@
         <v/>
       </c>
       <c r="G31" s="30">
-        <f>IF(C31="","",(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,C31)+1)/2)/COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C31="","",(COUNTIFS($D$2:$D$45,D31,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$45,D31,$C$2:$C$45,C31)+1)/2)/COUNTIFS($D$2:$D$45,D31,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H31">
@@ -3735,7 +3762,7 @@
         <v/>
       </c>
       <c r="G32" s="30">
-        <f>IF(C32="","",(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,C32)+1)/2)/COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C32="","",(COUNTIFS($D$2:$D$45,D32,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$45,D32,$C$2:$C$45,C32)+1)/2)/COUNTIFS($D$2:$D$45,D32,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H32">
@@ -3777,7 +3804,7 @@
         <v/>
       </c>
       <c r="G33" s="30">
-        <f>IF(C33="","",(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,C33)+1)/2)/COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C33="","",(COUNTIFS($D$2:$D$45,D33,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$45,D33,$C$2:$C$45,C33)+1)/2)/COUNTIFS($D$2:$D$45,D33,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H33">
@@ -3788,7 +3815,10 @@
         <f>IFERROR(B37/B33-1,"")</f>
         <v/>
       </c>
-      <c r="J33" s="30" t="n"/>
+      <c r="J33" s="30">
+        <f>IFERROR((B45/B33)^(1/3)-1,"")</f>
+        <v/>
+      </c>
       <c r="K33" s="30" t="n"/>
       <c r="L33" s="30" t="n"/>
     </row>
@@ -3816,7 +3846,7 @@
         <v/>
       </c>
       <c r="G34" s="30">
-        <f>IF(C34="","",(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,C34)+1)/2)/COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C34="","",(COUNTIFS($D$2:$D$45,D34,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$45,D34,$C$2:$C$45,C34)+1)/2)/COUNTIFS($D$2:$D$45,D34,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H34">
@@ -3855,7 +3885,7 @@
         <v/>
       </c>
       <c r="G35" s="30">
-        <f>IF(C35="","",(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,C35)+1)/2)/COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C35="","",(COUNTIFS($D$2:$D$45,D35,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$45,D35,$C$2:$C$45,C35)+1)/2)/COUNTIFS($D$2:$D$45,D35,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H35">
@@ -3894,7 +3924,7 @@
         <v/>
       </c>
       <c r="G36" s="30">
-        <f>IF(C36="","",(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,C36)+1)/2)/COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C36="","",(COUNTIFS($D$2:$D$45,D36,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$45,D36,$C$2:$C$45,C36)+1)/2)/COUNTIFS($D$2:$D$45,D36,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H36">
@@ -3933,7 +3963,7 @@
         <v/>
       </c>
       <c r="G37" s="30">
-        <f>IF(C37="","",(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,C37)+1)/2)/COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C37="","",(COUNTIFS($D$2:$D$45,D37,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$45,D37,$C$2:$C$45,C37)+1)/2)/COUNTIFS($D$2:$D$45,D37,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H37">
@@ -3972,7 +4002,7 @@
         <v/>
       </c>
       <c r="G38" s="30">
-        <f>IF(C38="","",(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,C38)+1)/2)/COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C38="","",(COUNTIFS($D$2:$D$45,D38,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$45,D38,$C$2:$C$45,C38)+1)/2)/COUNTIFS($D$2:$D$45,D38,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H38">
@@ -4011,7 +4041,7 @@
         <v/>
       </c>
       <c r="G39" s="30">
-        <f>IF(C39="","",(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,C39)+1)/2)/COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C39="","",(COUNTIFS($D$2:$D$45,D39,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$45,D39,$C$2:$C$45,C39)+1)/2)/COUNTIFS($D$2:$D$45,D39,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H39">
@@ -4050,7 +4080,7 @@
         <v/>
       </c>
       <c r="G40" s="30">
-        <f>IF(C40="","",(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,C40)+1)/2)/COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C40="","",(COUNTIFS($D$2:$D$45,D40,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$45,D40,$C$2:$C$45,C40)+1)/2)/COUNTIFS($D$2:$D$45,D40,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H40">
@@ -4089,14 +4119,17 @@
         <v/>
       </c>
       <c r="G41" s="30">
-        <f>IF(C41="","",(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,C41)+1)/2)/COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C41="","",(COUNTIFS($D$2:$D$45,D41,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$45,D41,$C$2:$C$45,C41)+1)/2)/COUNTIFS($D$2:$D$45,D41,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H41">
         <f>IF(G41="","",IF(G41&lt;=20%,"Q1 Cheapest",IF(G41&lt;=40%,"Q2",IF(G41&lt;=60%,"Q3",IF(G41&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I41" s="30" t="n"/>
+      <c r="I41" s="30">
+        <f>IFERROR(B45/B41-1,"")</f>
+        <v/>
+      </c>
       <c r="J41" s="30" t="n"/>
       <c r="K41" s="30" t="n"/>
       <c r="L41" s="30" t="n"/>
@@ -4125,7 +4158,7 @@
         <v/>
       </c>
       <c r="G42" s="30">
-        <f>IF(C42="","",(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,C42)+1)/2)/COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C42="","",(COUNTIFS($D$2:$D$45,D42,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$45,D42,$C$2:$C$45,C42)+1)/2)/COUNTIFS($D$2:$D$45,D42,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H42">
@@ -4161,7 +4194,7 @@
         <v/>
       </c>
       <c r="G43" s="30">
-        <f>IF(C43="","",(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,C43)+1)/2)/COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C43="","",(COUNTIFS($D$2:$D$45,D43,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$45,D43,$C$2:$C$45,C43)+1)/2)/COUNTIFS($D$2:$D$45,D43,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H43">
@@ -4197,7 +4230,7 @@
         <v/>
       </c>
       <c r="G44" s="30">
-        <f>IF(C44="","",(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,C44)+1)/2)/COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C44="","",(COUNTIFS($D$2:$D$45,D44,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$45,D44,$C$2:$C$45,C44)+1)/2)/COUNTIFS($D$2:$D$45,D44,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H44">
@@ -4208,6 +4241,42 @@
       <c r="J44" s="30" t="n"/>
       <c r="K44" s="30" t="n"/>
       <c r="L44" s="30" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B45" s="24" t="n">
+        <v>9360.4</v>
+      </c>
+      <c r="C45" s="25" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated</t>
+        </is>
+      </c>
+      <c r="E45" s="33">
+        <f>IFERROR(B45/C45,"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="30">
+        <f>IF(AND(D45=D41,E41&lt;&gt;""),E45/E41-1,"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="30">
+        <f>IF(C45="","",(COUNTIFS($D$2:$D$45,D45,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C45)+(COUNTIFS($D$2:$D$45,D45,$C$2:$C$45,C45)+1)/2)/COUNTIFS($D$2:$D$45,D45,$C$2:$C$45,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="H45">
+        <f>IF(G45="","",IF(G45&lt;=20%,"Q1 Cheapest",IF(G45&lt;=40%,"Q2",IF(G45&lt;=60%,"Q3",IF(G45&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
+        <v/>
+      </c>
+      <c r="I45" s="30" t="n"/>
+      <c r="J45" s="30" t="n"/>
+      <c r="K45" s="30" t="n"/>
+      <c r="L45" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4222,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4230,7 +4299,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
@@ -4544,6 +4613,39 @@
       </c>
       <c r="I9">
         <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>9360.4</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>0.597014925373</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>0.08101195846589999</v>
+      </c>
+      <c r="F10" s="34">
+        <f>IF(D10="","",100*(1-D10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="34">
+        <f>IF(E10="","",IF(E10&lt;=0,20,IF(E10&lt;5%,20+400*E10,IF(E10&lt;10%,40+400*(E10-5%),IF(E10&lt;15%,60+400*(E10-10%),IF(E10&lt;25%,80+200*(E10-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="34">
+        <f>IF(OR(F10="",G10=""),"",70%*F10+30%*G10)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4584,7 +4686,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-29</t>
+          <t>Retrieved 2026-09-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9360.4</v>
+        <v>9208.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>10.54</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5970149253731343</v>
+        <v>0.5746268656716418</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>888.0834914611006</v>
+        <v>888.0086788813886</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.08101195846594234</v>
+        <v>0.08153802731048954</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.09487666034155598</v>
+        <v>0.09643201542912247</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>40.29850746268657</v>
+        <v>42.53731343283582</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>52.40478338637693</v>
+        <v>52.61521092419581</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>43.93039023979368</v>
+        <v>45.56068268024381</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.272306730071805</v>
+        <v>7.278258823284395</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6458.415551818229</v>
+        <v>6463.157002221586</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.3100278244713657</v>
+        <v>-0.2981428328558924</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>11.11435126345729</v>
+        <v>11.11673210074233</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9870.471875376246</v>
+        <v>9871.754586258519</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.05449252973978114</v>
+        <v>0.07200888146020534</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4646,6 +4646,39 @@
       </c>
       <c r="I10">
         <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>9208.65</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>0.5746268656720001</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>0.0815380273105</v>
+      </c>
+      <c r="F11" s="34">
+        <f>IF(D11="","",100*(1-D11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="34">
+        <f>IF(E11="","",IF(E11&lt;=0,20,IF(E11&lt;5%,20+400*E11,IF(E11&lt;10%,40+400*(E11-5%),IF(E11&lt;15%,60+400*(E11-10%),IF(E11&lt;25%,80+200*(E11-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="34">
+        <f>IF(OR(F11="",G11=""),"",70%*F11+30%*G11)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4686,7 +4719,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-30</t>
+          <t>Retrieved 2026-10-01</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9208.65</v>
+        <v>9283.549999999999</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>10.37</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5746268656716418</v>
+        <v>0.5895522388059702</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>888.0086788813886</v>
+        <v>888.377990430622</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.08153802731048954</v>
+        <v>0.08188181476955347</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.09643201542912247</v>
+        <v>0.09569377990430622</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>42.53731343283582</v>
+        <v>41.04477611940298</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>52.61521092419581</v>
+        <v>52.75272590782139</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>45.56068268024381</v>
+        <v>44.5571610559285</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.278258823284395</v>
+        <v>7.282148532821233</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6463.157002221586</v>
+        <v>6469.300479605029</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2981428328558924</v>
+        <v>-0.3031436810697384</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>11.11673210074233</v>
+        <v>11.11828798455707</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9871.754586258519</v>
+        <v>9877.242336749738</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.07200888146020534</v>
+        <v>0.0639510033068964</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4679,6 +4679,39 @@
       </c>
       <c r="I11">
         <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>9283.549999999999</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>0.5895522388060001</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>0.08188181476960001</v>
+      </c>
+      <c r="F12" s="34">
+        <f>IF(D12="","",100*(1-D12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="34">
+        <f>IF(E12="","",IF(E12&lt;=0,20,IF(E12&lt;5%,20+400*E12,IF(E12&lt;10%,40+400*(E12-5%),IF(E12&lt;15%,60+400*(E12-10%),IF(E12&lt;25%,80+200*(E12-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="34">
+        <f>IF(OR(F12="",G12=""),"",70%*F12+30%*G12)</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4719,7 +4752,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-01</t>
+          <t>Retrieved 2026-10-05</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9283.549999999999</v>
+        <v>9346.450000000001</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>10.45</v>
+        <v>10.52</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>888.377990430622</v>
+        <v>888.4458174904944</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.08188181476955347</v>
+        <v>0.08198498621715178</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.09569377990430622</v>
+        <v>0.09505703422053233</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>52.75272590782139</v>
+        <v>52.79399448686071</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>44.5571610559285</v>
+        <v>44.5695416296403</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.282148532821233</v>
+        <v>7.283315844056918</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6469.300479605029</v>
+        <v>6470.831499114618</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.3031436810697384</v>
+        <v>-0.3076695965725363</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>11.11828798455707</v>
+        <v>11.11875490905134</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9877.242336749738</v>
+        <v>9878.411294648564</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.0639510033068964</v>
+        <v>0.05691586587940489</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4712,6 +4712,39 @@
       </c>
       <c r="I12">
         <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>9346.450000000001</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>0.5895522388060001</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>0.0819849862172</v>
+      </c>
+      <c r="F13" s="34">
+        <f>IF(D13="","",100*(1-D13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="34">
+        <f>IF(E13="","",IF(E13&lt;=0,20,IF(E13&lt;5%,20+400*E13,IF(E13&lt;10%,40+400*(E13-5%),IF(E13&lt;15%,60+400*(E13-10%),IF(E13&lt;25%,80+200*(E13-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="34">
+        <f>IF(OR(F13="",G13=""),"",70%*F13+30%*G13)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4752,7 +4785,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-05</t>
+          <t>Retrieved 2026-10-06</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9346.450000000001</v>
+        <v>9232.35</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>10.52</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5895522388059702</v>
+        <v>0.5746268656716418</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>888.4458174904944</v>
+        <v>888.5803657362849</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.08198498621715178</v>
+        <v>0.08188851958263865</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.09505703422053233</v>
+        <v>0.09624639076034648</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>41.04477611940298</v>
+        <v>42.53731343283582</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>52.79399448686071</v>
+        <v>52.75540783305546</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>44.5695416296403</v>
+        <v>45.60274175290171</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.283315844056918</v>
+        <v>7.282224392992139</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6470.831499114618</v>
+        <v>6470.84161449865</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.3076695965725363</v>
+        <v>-0.2991121854675517</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>11.11875490905134</v>
+        <v>11.11831832862543</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9878.411294648564</v>
+        <v>9879.51936682242</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.05691586587940489</v>
+        <v>0.07009801045480502</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4745,6 +4745,39 @@
       </c>
       <c r="I13">
         <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>9232.35</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>0.5746268656720001</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>0.0818885195826</v>
+      </c>
+      <c r="F14" s="34">
+        <f>IF(D14="","",100*(1-D14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="34">
+        <f>IF(E14="","",IF(E14&lt;=0,20,IF(E14&lt;5%,20+400*E14,IF(E14&lt;10%,40+400*(E14-5%),IF(E14&lt;15%,60+400*(E14-10%),IF(E14&lt;25%,80+200*(E14-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="34">
+        <f>IF(OR(F14="",G14=""),"",70%*F14+30%*G14)</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4785,7 +4818,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-06</t>
+          <t>Retrieved 2026-10-07</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9232.35</v>
+        <v>9010.450000000001</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>10.39</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5746268656716418</v>
+        <v>0.5149253731343284</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>888.5803657362849</v>
+        <v>887.7290640394089</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.08188851958263865</v>
+        <v>0.08044633246126542</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.09624639076034648</v>
+        <v>0.09852216748768472</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>42.53731343283582</v>
+        <v>48.50746268656716</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>52.75540783305546</v>
+        <v>52.17853298450617</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>45.60274175290171</v>
+        <v>49.60878377594887</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.282224392992139</v>
+        <v>7.265907075847459</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6470.84161449865</v>
+        <v>6450.156887839383</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2991121854675517</v>
+        <v>-0.2841470861234031</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>11.11831832862543</v>
+        <v>11.11179140176756</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9879.51936682242</v>
+        <v>9864.260180892265</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.07009801045480502</v>
+        <v>0.09475777357315818</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4778,6 +4778,39 @@
       </c>
       <c r="I14">
         <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B15" s="24" t="n">
+        <v>9010.450000000001</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0.514925373134</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>0.08044633246129999</v>
+      </c>
+      <c r="F15" s="34">
+        <f>IF(D15="","",100*(1-D15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="34">
+        <f>IF(E15="","",IF(E15&lt;=0,20,IF(E15&lt;5%,20+400*E15,IF(E15&lt;10%,40+400*(E15-5%),IF(E15&lt;15%,60+400*(E15-10%),IF(E15&lt;25%,80+200*(E15-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="34">
+        <f>IF(OR(F15="",G15=""),"",70%*F15+30%*G15)</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4818,7 +4851,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-07</t>
+          <t>Retrieved 2026-10-08</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9010.450000000001</v>
+        <v>9077.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>10.15</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5149253731343284</v>
+        <v>0.5298507462686567</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>887.7290640394089</v>
+        <v>888.2338551859099</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.08044633246126542</v>
+        <v>0.08096562279455899</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.09852216748768472</v>
+        <v>0.09784735812133072</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>48.50746268656716</v>
+        <v>47.01492537313433</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>52.17853298450617</v>
+        <v>52.3862491178236</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>49.60878377594887</v>
+        <v>48.62632249654111</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.265907075847459</v>
+        <v>7.27178247504701</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6450.156887839383</v>
+        <v>6459.043381884343</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2841470861234031</v>
+        <v>-0.2884752959836586</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>11.11179140176756</v>
+        <v>11.11414156144737</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9864.260180892265</v>
+        <v>9871.956806206348</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.09475777357315818</v>
+        <v>0.0874893895741069</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4811,6 +4811,39 @@
       </c>
       <c r="I15">
         <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>9077.75</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>0.529850746269</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>0.0809656227946</v>
+      </c>
+      <c r="F16" s="34">
+        <f>IF(D16="","",100*(1-D16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="34">
+        <f>IF(E16="","",IF(E16&lt;=0,20,IF(E16&lt;5%,20+400*E16,IF(E16&lt;10%,40+400*(E16-5%),IF(E16&lt;15%,60+400*(E16-10%),IF(E16&lt;25%,80+200*(E16-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="34">
+        <f>IF(OR(F16="",G16=""),"",70%*F16+30%*G16)</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4851,7 +4884,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-08</t>
+          <t>Retrieved 2026-10-09</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9077.75</v>
+        <v>9098.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>10.22</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>888.2338551859099</v>
+        <v>888.53515625</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.08096562279455899</v>
+        <v>0.08187564886304055</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.09784735812133072</v>
+        <v>0.09765625</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>52.3862491178236</v>
+        <v>52.75025954521622</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>48.62632249654111</v>
+        <v>48.73552562475889</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.27178247504701</v>
+        <v>7.282078769993259</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6459.043381884343</v>
+        <v>6470.382997720768</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2884752959836586</v>
+        <v>-0.2888594951178458</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>11.11414156144737</v>
+        <v>11.11826007942588</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9871.956806206348</v>
+        <v>9878.964956900807</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.0874893895741069</v>
+        <v>0.08576758588143307</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4844,6 +4844,39 @@
       </c>
       <c r="I16">
         <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <v>9098.6</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>0.529850746269</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>0.081875648863</v>
+      </c>
+      <c r="F17" s="34">
+        <f>IF(D17="","",100*(1-D17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="34">
+        <f>IF(E17="","",IF(E17&lt;=0,20,IF(E17&lt;5%,20+400*E17,IF(E17&lt;10%,40+400*(E17-5%),IF(E17&lt;15%,60+400*(E17-10%),IF(E17&lt;25%,80+200*(E17-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H17" s="34">
+        <f>IF(OR(F17="",G17=""),"",70%*F17+30%*G17)</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4884,7 +4917,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-09</t>
+          <t>Retrieved 2026-10-12</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9098.6</v>
+        <v>9196.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>10.24</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5298507462686567</v>
+        <v>0.5671641791044776</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>888.53515625</v>
+        <v>888.5603864734301</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.08187564886304055</v>
+        <v>0.08154009978118038</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.09765625</v>
+        <v>0.0966183574879227</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>47.01492537313433</v>
+        <v>43.28358208955224</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>52.75025954521622</v>
+        <v>52.61603991247215</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>48.73552562475889</v>
+        <v>46.08331943642821</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.282078769993259</v>
+        <v>7.278282271809926</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6470.382997720768</v>
+        <v>6467.193308302143</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2888594951178458</v>
+        <v>-0.2967843215642583</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>11.11826007942588</v>
+        <v>11.11674148015254</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9878.964956900807</v>
+        <v>9877.896105929554</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.08576758588143307</v>
+        <v>0.07408130243019739</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4877,6 +4877,39 @@
       </c>
       <c r="I17">
         <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B18" s="24" t="n">
+        <v>9196.6</v>
+      </c>
+      <c r="C18" s="25" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>0.567164179104</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>0.0815400997812</v>
+      </c>
+      <c r="F18" s="34">
+        <f>IF(D18="","",100*(1-D18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="34">
+        <f>IF(E18="","",IF(E18&lt;=0,20,IF(E18&lt;5%,20+400*E18,IF(E18&lt;10%,40+400*(E18-5%),IF(E18&lt;15%,60+400*(E18-10%),IF(E18&lt;25%,80+200*(E18-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H18" s="34">
+        <f>IF(OR(F18="",G18=""),"",70%*F18+30%*G18)</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4917,7 +4950,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-12</t>
+          <t>Retrieved 2026-10-13</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9196.6</v>
+        <v>9280.799999999999</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>10.35</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5671641791044776</v>
+        <v>0.5895522388059702</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>888.5603864734301</v>
+        <v>888.1148325358852</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.08154009978118038</v>
+        <v>0.08095657761564423</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0966183574879227</v>
+        <v>0.09569377990430622</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>43.28358208955224</v>
+        <v>41.04477611940298</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>52.61603991247215</v>
+        <v>52.38263104625769</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>46.08331943642821</v>
+        <v>44.4461325974594</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.278282271809926</v>
+        <v>7.271680135308431</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6467.193308302143</v>
+        <v>6458.08698562397</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2967843215642583</v>
+        <v>-0.3041454415972793</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>11.11674148015254</v>
+        <v>11.11410062555194</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9877.896105929554</v>
+        <v>9870.597615849041</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.07408130243019739</v>
+        <v>0.06355029909587984</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4910,6 +4910,39 @@
       </c>
       <c r="I18">
         <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <v>9280.799999999999</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>0.5895522388060001</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>0.0809565776156</v>
+      </c>
+      <c r="F19" s="34">
+        <f>IF(D19="","",100*(1-D19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="34">
+        <f>IF(E19="","",IF(E19&lt;=0,20,IF(E19&lt;5%,20+400*E19,IF(E19&lt;10%,40+400*(E19-5%),IF(E19&lt;15%,60+400*(E19-10%),IF(E19&lt;25%,80+200*(E19-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H19" s="34">
+        <f>IF(OR(F19="",G19=""),"",70%*F19+30%*G19)</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4950,7 +4983,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-13</t>
+          <t>Retrieved 2026-10-14</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9280.799999999999</v>
+        <v>9257.15</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>10.45</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5895522388059702</v>
+        <v>0.5746268656716418</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>888.1148325358852</v>
+        <v>889.2555235350624</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.08095657761564423</v>
+        <v>0.08225095656539927</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.09569377990430622</v>
+        <v>0.09606147934678194</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>41.04477611940298</v>
+        <v>42.53731343283582</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>52.38263104625769</v>
+        <v>52.9003826261597</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>44.4461325974594</v>
+        <v>45.64623419083298</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.271680135308431</v>
+        <v>7.286325108568517</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6458.08698562397</v>
+        <v>6479.404849066767</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.3041454415972793</v>
+        <v>-0.3000648310693067</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>11.11410062555194</v>
+        <v>11.11995861485598</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9870.597615849041</v>
+        <v>9888.484619741979</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.06355029909587984</v>
+        <v>0.06819967481805733</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4943,6 +4943,39 @@
       </c>
       <c r="I19">
         <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>9257.15</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>0.5746268656720001</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>0.0822509565654</v>
+      </c>
+      <c r="F20" s="34">
+        <f>IF(D20="","",100*(1-D20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="34">
+        <f>IF(E20="","",IF(E20&lt;=0,20,IF(E20&lt;5%,20+400*E20,IF(E20&lt;10%,40+400*(E20-5%),IF(E20&lt;15%,60+400*(E20-10%),IF(E20&lt;25%,80+200*(E20-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H20" s="34">
+        <f>IF(OR(F20="",G20=""),"",70%*F20+30%*G20)</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4983,7 +5016,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-14</t>
+          <t>Retrieved 2026-10-15</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9257.15</v>
+        <v>9247.299999999999</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>10.41</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>889.2555235350624</v>
+        <v>890.019249278152</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.08225095656539927</v>
+        <v>0.0835040326826324</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.09606147934678194</v>
+        <v>0.09624639076034648</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>52.9003826261597</v>
+        <v>53.40161307305296</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>45.64623419083298</v>
+        <v>45.79660332490096</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.286325108568517</v>
+        <v>7.296301661868385</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6479.404849066767</v>
+        <v>6493.848927603032</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.3000648310693067</v>
+        <v>-0.29775729914645</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>11.11995861485598</v>
+        <v>11.12562967934083</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9888.484619741979</v>
+        <v>9902.02457495365</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.06819967481805733</v>
+        <v>0.07080170157274557</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4976,6 +4976,39 @@
       </c>
       <c r="I20">
         <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>9247.299999999999</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>0.5746268656720001</v>
+      </c>
+      <c r="E21" s="26" t="n">
+        <v>0.0835040326826</v>
+      </c>
+      <c r="F21" s="34">
+        <f>IF(D21="","",100*(1-D21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="34">
+        <f>IF(E21="","",IF(E21&lt;=0,20,IF(E21&lt;5%,20+400*E21,IF(E21&lt;10%,40+400*(E21-5%),IF(E21&lt;15%,60+400*(E21-10%),IF(E21&lt;25%,80+200*(E21-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="34">
+        <f>IF(OR(F21="",G21=""),"",70%*F21+30%*G21)</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5016,7 +5049,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-15</t>
+          <t>Retrieved 2026-10-16</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9247.299999999999</v>
+        <v>9190.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>10.39</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5746268656716418</v>
+        <v>0.5597014925373134</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>890.019249278152</v>
+        <v>889.699903194579</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.0835040326826324</v>
+        <v>0.08351403888955811</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.09624639076034648</v>
+        <v>0.0968054211035818</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>42.53731343283582</v>
+        <v>44.02985074626866</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>53.40161307305296</v>
+        <v>53.40561555582324</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>45.79660332490096</v>
+        <v>46.84258018913503</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.296301661868385</v>
+        <v>7.296369589718829</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6493.848927603032</v>
+        <v>6491.579317644711</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.29775729914645</v>
+        <v>-0.2936718693399004</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>11.12562967934083</v>
+        <v>11.12567496457446</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9902.02457495365</v>
+        <v>9898.511938956246</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.07080170157274557</v>
+        <v>0.07702565000720796</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5009,6 +5009,39 @@
       </c>
       <c r="I21">
         <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <v>9190.6</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>0.559701492537</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>0.0835140388896</v>
+      </c>
+      <c r="F22" s="34">
+        <f>IF(D22="","",100*(1-D22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="34">
+        <f>IF(E22="","",IF(E22&lt;=0,20,IF(E22&lt;5%,20+400*E22,IF(E22&lt;10%,40+400*(E22-5%),IF(E22&lt;15%,60+400*(E22-10%),IF(E22&lt;25%,80+200*(E22-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H22" s="34">
+        <f>IF(OR(F22="",G22=""),"",70%*F22+30%*G22)</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5049,7 +5082,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-16</t>
+          <t>Retrieved 2026-10-19</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9190.6</v>
+        <v>9094.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>10.33</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5597014925373134</v>
+        <v>0.5298507462686567</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>889.699903194579</v>
+        <v>889.8630136986301</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.08351403888955811</v>
+        <v>0.08180232929236575</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0968054211035818</v>
+        <v>0.09784735812133072</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>44.02985074626866</v>
+        <v>47.01492537313433</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>53.40561555582324</v>
+        <v>52.7209317169463</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>46.84258018913503</v>
+        <v>48.72672727627791</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.296369589718829</v>
+        <v>7.281249211422195</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6491.579317644711</v>
+        <v>6479.314366766928</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2936718693399004</v>
+        <v>-0.2875490008393156</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>11.12567496457446</v>
+        <v>11.11792825599745</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9898.511938956246</v>
+        <v>9893.433143967046</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.07702565000720796</v>
+        <v>0.08785990763184448</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5042,6 +5042,39 @@
       </c>
       <c r="I22">
         <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B23" s="24" t="n">
+        <v>9094.4</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>0.529850746269</v>
+      </c>
+      <c r="E23" s="26" t="n">
+        <v>0.0818023292924</v>
+      </c>
+      <c r="F23" s="34">
+        <f>IF(D23="","",100*(1-D23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="34">
+        <f>IF(E23="","",IF(E23&lt;=0,20,IF(E23&lt;5%,20+400*E23,IF(E23&lt;10%,40+400*(E23-5%),IF(E23&lt;15%,60+400*(E23-10%),IF(E23&lt;25%,80+200*(E23-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H23" s="34">
+        <f>IF(OR(F23="",G23=""),"",70%*F23+30%*G23)</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5082,7 +5115,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-19</t>
+          <t>Retrieved 2026-10-21</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9094.4</v>
+        <v>9034.35</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>10.22</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5298507462686567</v>
+        <v>0.5149253731343284</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>889.8630136986301</v>
+        <v>890.0837438423646</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.08180232929236575</v>
+        <v>0.08207066990205636</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.09784735812133072</v>
+        <v>0.09852216748768472</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>47.01492537313433</v>
+        <v>48.50746268656716</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>52.7209317169463</v>
+        <v>52.82826796082254</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>48.72672727627791</v>
+        <v>49.80370426884377</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.281249211422195</v>
+        <v>7.284285293748981</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6479.314366766928</v>
+        <v>6483.623925475972</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2875490008393156</v>
+        <v>-0.2823364242611841</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>11.11792825599745</v>
+        <v>11.11914268892816</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9893.433143967046</v>
+        <v>9896.968152878637</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.08785990763184448</v>
+        <v>0.09548203831804569</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5075,6 +5075,39 @@
       </c>
       <c r="I23">
         <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B24" s="24" t="n">
+        <v>9034.35</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>0.514925373134</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>0.0820706699021</v>
+      </c>
+      <c r="F24" s="34">
+        <f>IF(D24="","",100*(1-D24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="34">
+        <f>IF(E24="","",IF(E24&lt;=0,20,IF(E24&lt;5%,20+400*E24,IF(E24&lt;10%,40+400*(E24-5%),IF(E24&lt;15%,60+400*(E24-10%),IF(E24&lt;25%,80+200*(E24-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H24" s="34">
+        <f>IF(OR(F24="",G24=""),"",70%*F24+30%*G24)</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5115,7 +5148,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-21</t>
+          <t>Retrieved 2026-10-22</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9034.35</v>
+        <v>8885.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>10.15</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>890.0837438423646</v>
+        <v>889.4644644644644</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.08207066990205636</v>
+        <v>0.08083505657738366</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.09852216748768472</v>
+        <v>0.1001001001001001</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>52.82826796082254</v>
+        <v>52.33402263095346</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>49.80370426884377</v>
+        <v>49.65543066988305</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.284285293748981</v>
+        <v>7.270305211561255</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6483.623925475972</v>
+        <v>6466.678131494537</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2823364242611841</v>
+        <v>-0.272241720564439</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>11.11914268892816</v>
+        <v>11.11355065605307</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9896.968152878637</v>
+        <v>9885.108382584944</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.09548203831804569</v>
+        <v>0.1124675331384457</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5108,6 +5108,39 @@
       </c>
       <c r="I24">
         <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <v>8885.75</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>0.514925373134</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>0.08083505657740001</v>
+      </c>
+      <c r="F25" s="34">
+        <f>IF(D25="","",100*(1-D25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="34">
+        <f>IF(E25="","",IF(E25&lt;=0,20,IF(E25&lt;5%,20+400*E25,IF(E25&lt;10%,40+400*(E25-5%),IF(E25&lt;15%,60+400*(E25-10%),IF(E25&lt;25%,80+200*(E25-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H25" s="34">
+        <f>IF(OR(F25="",G25=""),"",70%*F25+30%*G25)</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5148,7 +5181,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-22</t>
+          <t>Retrieved 2026-10-23</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>8885.75</v>
+        <v>8984.950000000001</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>9.99</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>889.4644644644644</v>
+        <v>888.7190900098914</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.08083505657738366</v>
+        <v>0.07996425516195083</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.1001001001001001</v>
+        <v>0.09891196834817013</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>52.33402263095346</v>
+        <v>51.98570206478033</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>49.65543066988305</v>
+        <v>49.5509345000311</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.270305211561255</v>
+        <v>7.260452715546643</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6466.678131494537</v>
+        <v>6452.502930420457</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.272241720564439</v>
+        <v>-0.2818543308064645</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>11.11355065605307</v>
+        <v>11.10902414411807</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9885.108382584944</v>
+        <v>9872.801828258525</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1124675331384457</v>
+        <v>0.09881544452206459</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5141,6 +5141,39 @@
       </c>
       <c r="I25">
         <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <v>8984.950000000001</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>0.514925373134</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>0.07996425516199999</v>
+      </c>
+      <c r="F26" s="34">
+        <f>IF(D26="","",100*(1-D26))</f>
+        <v/>
+      </c>
+      <c r="G26" s="34">
+        <f>IF(E26="","",IF(E26&lt;=0,20,IF(E26&lt;5%,20+400*E26,IF(E26&lt;10%,40+400*(E26-5%),IF(E26&lt;15%,60+400*(E26-10%),IF(E26&lt;25%,80+200*(E26-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H26" s="34">
+        <f>IF(OR(F26="",G26=""),"",70%*F26+30%*G26)</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5181,7 +5214,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-23</t>
+          <t>Retrieved 2026-10-26</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>8984.950000000001</v>
+        <v>9048.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>10.11</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5149253731343284</v>
+        <v>0.5298507462686567</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>888.7190900098914</v>
+        <v>884.516129032258</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07996425516195083</v>
+        <v>0.07506467992489685</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.09891196834817013</v>
+        <v>0.09775171065493646</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>48.50746268656716</v>
+        <v>47.01492537313433</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>51.98570206478033</v>
+        <v>50.02587196995874</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>49.5509345000311</v>
+        <v>47.91820935218165</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.260452715546643</v>
+        <v>7.205017521435976</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6452.502930420457</v>
+        <v>6372.954207670144</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2818543308064645</v>
+        <v>-0.2956972119808431</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>11.10902414411807</v>
+        <v>11.0535889500074</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9872.801828258525</v>
+        <v>9777.07770997429</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.09881544452206459</v>
+        <v>0.0805072287397266</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5174,6 +5174,39 @@
       </c>
       <c r="I26">
         <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B27" s="24" t="n">
+        <v>9048.6</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>0.529850746269</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>0.0750646799249</v>
+      </c>
+      <c r="F27" s="34">
+        <f>IF(D27="","",100*(1-D27))</f>
+        <v/>
+      </c>
+      <c r="G27" s="34">
+        <f>IF(E27="","",IF(E27&lt;=0,20,IF(E27&lt;5%,20+400*E27,IF(E27&lt;10%,40+400*(E27-5%),IF(E27&lt;15%,60+400*(E27-10%),IF(E27&lt;25%,80+200*(E27-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H27" s="34">
+        <f>IF(OR(F27="",G27=""),"",70%*F27+30%*G27)</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5214,7 +5247,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-26</t>
+          <t>Retrieved 2026-10-27</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9048.6</v>
+        <v>8993.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>10.23</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>884.516129032258</v>
+        <v>880.8667972575905</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07506467992489685</v>
+        <v>0.04707026553396476</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.09775171065493646</v>
+        <v>0.0979431929480901</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>50.02587196995874</v>
+        <v>38.8281062135859</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>47.91820935218165</v>
+        <v>44.5588796252698</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>7.205017521435976</v>
+        <v>6.896733365364431</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6372.954207670144</v>
+        <v>6075.10343108813</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2956972119808431</v>
+        <v>-0.3245119132845807</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>11.0535889500074</v>
+        <v>10.45953736190271</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9777.07770997429</v>
+        <v>9213.459176775352</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.0805072287397266</v>
+        <v>0.02444048598459503</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5207,6 +5207,39 @@
       </c>
       <c r="I27">
         <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <v>8993.65</v>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>0.529850746269</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>0.047070265534</v>
+      </c>
+      <c r="F28" s="34">
+        <f>IF(D28="","",100*(1-D28))</f>
+        <v/>
+      </c>
+      <c r="G28" s="34">
+        <f>IF(E28="","",IF(E28&lt;=0,20,IF(E28&lt;5%,20+400*E28,IF(E28&lt;10%,40+400*(E28-5%),IF(E28&lt;15%,60+400*(E28-10%),IF(E28&lt;25%,80+200*(E28-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H28" s="34">
+        <f>IF(OR(F28="",G28=""),"",70%*F28+30%*G28)</f>
+        <v/>
+      </c>
+      <c r="I28">
+        <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5247,7 +5280,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-27</t>
+          <t>Retrieved 2026-10-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>8993.65</v>
+        <v>9097.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>10.21</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5298507462686567</v>
+        <v>0.5597014925373134</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>880.8667972575905</v>
+        <v>880.6485963213941</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.04707026553396476</v>
+        <v>0.04705602798191766</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0979431929480901</v>
+        <v>0.0968054211035818</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>47.01492537313433</v>
+        <v>44.02985074626866</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>38.8281062135859</v>
+        <v>38.82241119276706</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>44.5588796252698</v>
+        <v>42.46761888021818</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>6.896733365364431</v>
+        <v>6.896427298674139</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6075.10343108813</v>
+        <v>6073.329020209923</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.3245119132845807</v>
+        <v>-0.3323884512416129</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>10.45953736190271</v>
+        <v>10.45936016539781</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9213.459176775352</v>
+        <v>9211.020848077485</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.02444048598459503</v>
+        <v>0.01252276528536411</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5240,6 +5240,39 @@
       </c>
       <c r="I28">
         <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <v>9097.1</v>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>0.559701492537</v>
+      </c>
+      <c r="E29" s="26" t="n">
+        <v>0.0470560279819</v>
+      </c>
+      <c r="F29" s="34">
+        <f>IF(D29="","",100*(1-D29))</f>
+        <v/>
+      </c>
+      <c r="G29" s="34">
+        <f>IF(E29="","",IF(E29&lt;=0,20,IF(E29&lt;5%,20+400*E29,IF(E29&lt;10%,40+400*(E29-5%),IF(E29&lt;15%,60+400*(E29-10%),IF(E29&lt;25%,80+200*(E29-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H29" s="34">
+        <f>IF(OR(F29="",G29=""),"",70%*F29+30%*G29)</f>
+        <v/>
+      </c>
+      <c r="I29">
+        <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5280,7 +5313,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-28</t>
+          <t>Retrieved 2026-10-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pse.xlsx
+++ b/docs/downloads/indices/nifty-pse.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9097.1</v>
+        <v>9075.35</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>10.33</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5597014925373134</v>
+        <v>0.5298507462686567</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>880.6485963213941</v>
+        <v>884.5370370370371</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.04705602798191766</v>
+        <v>0.05156937206510159</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0968054211035818</v>
+        <v>0.09746588693957116</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>44.02985074626866</v>
+        <v>47.01492537313433</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>38.82241119276706</v>
+        <v>40.62774882604064</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>42.46761888021818</v>
+        <v>45.09877240900622</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>6.896427298674139</v>
+        <v>6.978695832584238</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>6073.329020209923</v>
+        <v>6172.91493413678</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.3323884512416129</v>
+        <v>-0.3198152209956884</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>10.45936016539781</v>
+        <v>10.51553195633023</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9211.020848077485</v>
+        <v>9301.377479520623</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.01252276528536411</v>
+        <v>0.02490564876513002</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5273,6 +5273,39 @@
       </c>
       <c r="I29">
         <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B30" s="24" t="n">
+        <v>9075.35</v>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>0.529850746269</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>0.0515693720651</v>
+      </c>
+      <c r="F30" s="34">
+        <f>IF(D30="","",100*(1-D30))</f>
+        <v/>
+      </c>
+      <c r="G30" s="34">
+        <f>IF(E30="","",IF(E30&lt;=0,20,IF(E30&lt;5%,20+400*E30,IF(E30&lt;10%,40+400*(E30-5%),IF(E30&lt;15%,60+400*(E30-10%),IF(E30&lt;25%,80+200*(E30-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H30" s="34">
+        <f>IF(OR(F30="",G30=""),"",70%*F30+30%*G30)</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>IF(H30="","",IF(H30&gt;=70,"BUY",IF(H30&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5313,7 +5346,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-29</t>
+          <t>Retrieved 2026-10-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
